--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4761.26</v>
+        <v>4720.94</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25184.65</v>
+        <v>25047</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4194.6</v>
+        <v>4189.26</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4655.98</v>
+        <v>4706.62</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2277.18</v>
+        <v>2301.95</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2712.74</v>
+        <v>2742.25</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2735.33</v>
+        <v>2748.07</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4544.87</v>
+        <v>4526.14</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2243.53</v>
+        <v>2240.05</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2225.15</v>
+        <v>2221.7</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>11308.59</v>
+        <v>11366.99</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4365.75</v>
+        <v>4309.32</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>37111.26</v>
+        <v>36639.87</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>6768.28</v>
+        <v>6682.31</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5425.06</v>
+        <v>5402.32</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>9032.59</v>
+        <v>8928.059999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>7023.47</v>
+        <v>6942.18</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2570.35</v>
+        <v>2548.57</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>2284.16</v>
+        <v>2264.81</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>822.79</v>
+        <v>825.9400000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>47828.19</v>
+        <v>48011.77</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>3622.38</v>
+        <v>3631.99</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1786.72</v>
+        <v>1791.46</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3044.71</v>
+        <v>3040.44</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>4522.38</v>
+        <v>4528.18</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>2779.11</v>
+        <v>2802.86</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>3720.77</v>
+        <v>3766.5</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>23813.06</v>
+        <v>24119.05</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>16483.75</v>
+        <v>16695.56</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17932.03</v>
+        <v>18030.09</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2399.48</v>
+        <v>2365.09</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>14172.65</v>
+        <v>13968.42</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7221.72</v>
+        <v>7207.5</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1256.82</v>
+        <v>1255.96</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6573.79</v>
+        <v>6569.3</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>9304.059999999999</v>
+        <v>9254.91</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>29148.99</v>
+        <v>29340.03</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5360.33</v>
+        <v>5432.52</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1635.91</v>
+        <v>1657.94</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>940.92</v>
+        <v>953.59</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>2147.91</v>
+        <v>2180.61</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1360.74</v>
+        <v>1381.46</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1685.67</v>
+        <v>1728.28</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1169.5</v>
+        <v>1204.97</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>817.8200000000001</v>
+        <v>842.62</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2782.62</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3749.91</v>
+        <v>3863.62</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2252.2</v>
+        <v>2320.5</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>828.89</v>
+        <v>854.02</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>9479.440000000001</v>
+        <v>9766.889999999999</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>802.27</v>
+        <v>826.12</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2545.27</v>
+        <v>2620.92</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2422.85</v>
+        <v>2414.23</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5779.37</v>
+        <v>5758.8</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3116.25</v>
+        <v>3105.16</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3004.77</v>
+        <v>2982.28</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>922.55</v>
+        <v>915.65</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1301</v>
+        <v>1304.76</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1732.04</v>
+        <v>1737.06</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3471.65</v>
+        <v>3481.7</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2016.09</v>
+        <v>2026.51</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>46851.86</v>
+        <v>47093.88</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2697.22</v>
+        <v>2711.15</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>9897.08</v>
+        <v>9948.209999999999</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>27428.45</v>
+        <v>27312.8</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2896.73</v>
+        <v>2904.68</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>2814.23</v>
+        <v>2839.83</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>868.71</v>
+        <v>876.61</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2780.41</v>
+        <v>2798.72</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>4268.09</v>
+        <v>4306.11</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2064.05</v>
+        <v>2082.43</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1736.94</v>
+        <v>1733.96</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1107.6</v>
+        <v>1105.7</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>4593.59</v>
+        <v>4585.72</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>814.95</v>
+        <v>809.11</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5275.01</v>
+        <v>5237.22</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>9519.41</v>
+        <v>9482.67</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2208.16</v>
+        <v>2199.64</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>67566.74000000001</v>
+        <v>67305.96000000001</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9831.4</v>
+        <v>9882.299999999999</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>836.86</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2503.74</v>
+        <v>2516.7</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>2160.53</v>
+        <v>2171.71</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>46138.81</v>
+        <v>46183.28</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>11061.63</v>
+        <v>11382.93</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2282.18</v>
+        <v>2291.18</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>3169.14</v>
+        <v>3181.63</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>7674.74</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1680.05</v>
+        <v>1686.68</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>920.84</v>
+        <v>936.02</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4557.72</v>
+        <v>4632.84</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>17377.48</v>
+        <v>17663.88</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2160.38</v>
+        <v>2132.57</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>37626.72</v>
+        <v>37361.19</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>26406.36</v>
+        <v>26220.01</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>10057.6</v>
+        <v>10239.95</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>1270.6</v>
+        <v>1293.64</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2728.23</v>
+        <v>2777.7</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>29775.76</v>
+        <v>30242.19</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>768.33</v>
+        <v>768.29</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>1141.15</v>
+        <v>1136.05</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>53098.54</v>
+        <v>52861.11</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1317.02</v>
+        <v>1311.13</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1387.55</v>
+        <v>1388.74</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>1296.07</v>
+        <v>1301.42</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3955.91</v>
+        <v>3944.99</v>
       </c>
     </row>
     <row r="108">
@@ -7039,7 +7039,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>139.98</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="109">
@@ -7100,7 +7100,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>7568.68</v>
+        <v>7481.3</v>
       </c>
     </row>
     <row r="110">
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>2382.56</v>
+        <v>2368.88</v>
       </c>
     </row>
     <row r="111">
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>800.12</v>
+        <v>795.53</v>
       </c>
     </row>
     <row r="112">
@@ -7283,7 +7283,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>2922.51</v>
+        <v>2905.72</v>
       </c>
     </row>
     <row r="113">
@@ -7344,7 +7344,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>864.9299999999999</v>
+        <v>859.96</v>
       </c>
     </row>
     <row r="114">
@@ -7405,7 +7405,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>35321.38</v>
+        <v>35118.49</v>
       </c>
     </row>
     <row r="115">
@@ -7466,7 +7466,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>1743.23</v>
+        <v>1733.21</v>
       </c>
     </row>
     <row r="116">
@@ -7527,7 +7527,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>4057.62</v>
+        <v>4031.63</v>
       </c>
     </row>
     <row r="117">
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>8586.58</v>
+        <v>8531.57</v>
       </c>
     </row>
     <row r="118">
@@ -7649,7 +7649,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2660.79</v>
+        <v>2649.32</v>
       </c>
     </row>
     <row r="119">
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1784.35</v>
+        <v>1776.67</v>
       </c>
     </row>
     <row r="120">
@@ -7771,7 +7771,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6769.26</v>
+        <v>6671.33</v>
       </c>
     </row>
     <row r="121">
@@ -7832,7 +7832,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>2880.36</v>
+        <v>2838.69</v>
       </c>
     </row>
     <row r="122">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3647.56</v>
+        <v>3569.08</v>
       </c>
     </row>
     <row r="123">
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>2937.34</v>
+        <v>2868.99</v>
       </c>
     </row>
     <row r="124">
@@ -8015,7 +8015,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>982.3</v>
+        <v>959.4400000000001</v>
       </c>
     </row>
     <row r="125">
@@ -8076,7 +8076,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>42717.04</v>
+        <v>41354.92</v>
       </c>
     </row>
     <row r="126">
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>790.92</v>
+        <v>765.7</v>
       </c>
     </row>
     <row r="127">
@@ -8198,7 +8198,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2015.32</v>
+        <v>1951.06</v>
       </c>
     </row>
     <row r="128">
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>1757.39</v>
+        <v>1701.36</v>
       </c>
     </row>
     <row r="129">
@@ -8320,7 +8320,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>53396.3</v>
+        <v>51693.65</v>
       </c>
     </row>
     <row r="130">
@@ -8381,7 +8381,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>3382.06</v>
+        <v>3315.36</v>
       </c>
     </row>
     <row r="131">
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>2695.43</v>
+        <v>2646.55</v>
       </c>
     </row>
     <row r="132">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1228.75</v>
+        <v>1206.46</v>
       </c>
     </row>
     <row r="133">
@@ -8564,7 +8564,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>870</v>
+        <v>872.53</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>35601.81</v>
+        <v>35542.28</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>25605.47</v>
+        <v>25562.66</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>7009.27</v>
+        <v>7095.54</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>6063.37</v>
+        <v>6142.49</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>13722.07</v>
+        <v>13901.14</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3800</v>
+        <v>3871.87</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>27976.66</v>
+        <v>28505.77</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>30968.71</v>
+        <v>31320.89</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1649.58</v>
+        <v>1660.13</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>4967.28</v>
+        <v>4987.86</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1715.91</v>
+        <v>1723.02</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2414.12</v>
+        <v>2424.13</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>3750.38</v>
+        <v>3765.92</v>
       </c>
     </row>
     <row r="147">
@@ -9418,7 +9418,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>4028.87</v>
+        <v>4037.22</v>
       </c>
     </row>
     <row r="148">
@@ -9479,7 +9479,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>5061.55</v>
+        <v>5039.81</v>
       </c>
     </row>
     <row r="149">
@@ -9540,7 +9540,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>21822.37</v>
+        <v>21728.62</v>
       </c>
     </row>
     <row r="150">
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>7472.5</v>
+        <v>7440.4</v>
       </c>
     </row>
     <row r="151">
@@ -9662,7 +9662,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>3141.28</v>
+        <v>3158.19</v>
       </c>
     </row>
     <row r="152">
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>16715.77</v>
+        <v>16902.72</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>5036.15</v>
+        <v>5074.29</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4932.89</v>
+        <v>4970.25</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>11962.49</v>
+        <v>12053.09</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>12039.49</v>
+        <v>12129.19</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>28104.87</v>
+        <v>28314.25</v>
       </c>
     </row>
     <row r="158">
@@ -10089,7 +10089,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1656.37</v>
+        <v>1649.11</v>
       </c>
     </row>
     <row r="159">
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>4788.72</v>
+        <v>4736.63</v>
       </c>
     </row>
     <row r="160">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>1163.83</v>
+        <v>1151.17</v>
       </c>
     </row>
     <row r="161">
@@ -10272,7 +10272,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1746.11</v>
+        <v>1742.15</v>
       </c>
     </row>
     <row r="162">
@@ -10333,7 +10333,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>2623.7</v>
+        <v>2617.22</v>
       </c>
     </row>
     <row r="163">
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>811.98</v>
+        <v>809.98</v>
       </c>
     </row>
     <row r="164">
@@ -10455,7 +10455,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>27359.82</v>
+        <v>27446.9</v>
       </c>
     </row>
     <row r="165">
@@ -10516,7 +10516,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>832.96</v>
+        <v>844.88</v>
       </c>
     </row>
     <row r="166">
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1533.04</v>
+        <v>1554.97</v>
       </c>
     </row>
     <row r="167">
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>32690.54</v>
+        <v>33243.42</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>16812.99</v>
+        <v>16983.97</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>869.22</v>
+        <v>877.37</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>6755.22</v>
+        <v>6662.4</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>10974.69</v>
+        <v>10823.9</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3133.59</v>
+        <v>3090.53</v>
       </c>
     </row>
     <row r="173">
@@ -11004,7 +11004,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>842.54</v>
+        <v>830.96</v>
       </c>
     </row>
     <row r="174">
@@ -11065,7 +11065,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1794.87</v>
+        <v>1783.74</v>
       </c>
     </row>
     <row r="175">
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>955.5</v>
+        <v>949.58</v>
       </c>
     </row>
     <row r="176">
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>794.9</v>
+        <v>810.01</v>
       </c>
     </row>
     <row r="177">
@@ -11248,7 +11248,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>5043.83</v>
+        <v>5139.73</v>
       </c>
     </row>
     <row r="178">
@@ -11309,7 +11309,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>11745.35</v>
+        <v>12010.24</v>
       </c>
     </row>
     <row r="179">
@@ -11370,7 +11370,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4388.55</v>
+        <v>4487.52</v>
       </c>
     </row>
     <row r="180">
@@ -11431,7 +11431,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>2411.72</v>
+        <v>2428.37</v>
       </c>
     </row>
     <row r="181">
@@ -11492,7 +11492,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>909.09</v>
+        <v>911.9</v>
       </c>
     </row>
     <row r="182">
@@ -11553,7 +11553,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>800.11</v>
+        <v>789.45</v>
       </c>
     </row>
     <row r="183">
@@ -11614,7 +11614,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>791.54</v>
+        <v>781</v>
       </c>
     </row>
     <row r="184">
@@ -11675,7 +11675,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>21174.06</v>
+        <v>20759.6</v>
       </c>
     </row>
     <row r="185">
@@ -11736,7 +11736,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>25323.18</v>
+        <v>24827.51</v>
       </c>
     </row>
     <row r="186">
@@ -11797,7 +11797,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>943.99</v>
+        <v>924.59</v>
       </c>
     </row>
     <row r="187">
@@ -11858,7 +11858,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>5131.23</v>
+        <v>5179.97</v>
       </c>
     </row>
     <row r="188">
@@ -11919,7 +11919,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>3327.6</v>
+        <v>3340.58</v>
       </c>
     </row>
     <row r="189">
@@ -11980,7 +11980,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>3312.77</v>
+        <v>3346.09</v>
       </c>
     </row>
     <row r="190">
@@ -12041,7 +12041,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>26353.41</v>
+        <v>26618.46</v>
       </c>
     </row>
     <row r="191">
@@ -12102,7 +12102,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>26351.67</v>
+        <v>26407.83</v>
       </c>
     </row>
     <row r="192">
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>11424.74</v>
+        <v>11449.09</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>15291.67</v>
+        <v>15324.27</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>1388.17</v>
+        <v>1391.12</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>4029.47</v>
+        <v>4055.74</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2406.82</v>
+        <v>2422.51</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>11014.82</v>
+        <v>11040.08</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>10736.29</v>
+        <v>10760.91</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>1226.42</v>
+        <v>1234.63</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1078.45</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="201">
@@ -12716,7 +12716,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>108773.97</v>
+        <v>108430.38</v>
       </c>
     </row>
     <row r="202">
@@ -12777,7 +12777,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>831.4</v>
+        <v>828.78</v>
       </c>
     </row>
     <row r="203">
@@ -12838,7 +12838,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1073.08</v>
+        <v>1070.74</v>
       </c>
     </row>
     <row r="204">
@@ -12899,7 +12899,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4998.24</v>
+        <v>4988.22</v>
       </c>
     </row>
     <row r="205">
@@ -12960,7 +12960,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>45873.52</v>
+        <v>45781.56</v>
       </c>
     </row>
     <row r="206">
@@ -13021,7 +13021,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>2095.26</v>
+        <v>2091.06</v>
       </c>
     </row>
     <row r="207">
@@ -13082,7 +13082,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>8232.799999999999</v>
+        <v>8216.299999999999</v>
       </c>
     </row>
     <row r="208">
@@ -13143,7 +13143,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>8898.32</v>
+        <v>8846.809999999999</v>
       </c>
     </row>
     <row r="209">
@@ -13204,7 +13204,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1074.79</v>
+        <v>1057.45</v>
       </c>
     </row>
     <row r="210">
@@ -13265,7 +13265,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>8315.77</v>
+        <v>8181.57</v>
       </c>
     </row>
     <row r="211">
@@ -13326,7 +13326,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>2361.95</v>
+        <v>2323.84</v>
       </c>
     </row>
     <row r="212">
@@ -13387,7 +13387,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>6841.22</v>
+        <v>6730.82</v>
       </c>
     </row>
     <row r="213">
@@ -13448,7 +13448,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>892.98</v>
+        <v>878.5700000000001</v>
       </c>
     </row>
     <row r="214">
@@ -13509,7 +13509,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>12727.84</v>
+        <v>12579.75</v>
       </c>
     </row>
     <row r="215">
@@ -13570,7 +13570,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1662.85</v>
+        <v>1653.63</v>
       </c>
     </row>
     <row r="216">
@@ -13631,7 +13631,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1453.13</v>
+        <v>1462.85</v>
       </c>
     </row>
     <row r="217">
@@ -13692,7 +13692,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2845.49</v>
+        <v>2864.54</v>
       </c>
     </row>
     <row r="218">
@@ -13753,7 +13753,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>5019.71</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="219">
@@ -13814,7 +13814,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>789.02</v>
+        <v>794.3</v>
       </c>
     </row>
     <row r="220">
@@ -13875,7 +13875,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>860.98</v>
+        <v>866.74</v>
       </c>
     </row>
     <row r="221">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>9662.25</v>
+        <v>9726.92</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
@@ -562,7 +562,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>76.872.717-1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1273,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1338,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1403,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1468,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1533,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1659,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1846,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1911,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1976,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2041,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2106,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2171,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2236,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2301,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2366,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2431,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2496,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2683,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2748,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2813,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2878,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2943,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3069,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3134,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3260,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3325,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3390,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3455,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3520,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3646,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3711,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3776,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3902,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3967,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4032,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4097,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4162,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4227,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4292,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4418,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4544,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4609,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4674,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4800,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4926,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5056,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5121,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5186,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5251,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5316,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5381,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5446,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5698,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5824,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5950,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6015,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6141,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6206,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6271,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6336,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6401,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6531,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6596,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6661,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6726,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6791,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6856,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6982,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7047,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7177,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7242,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7307,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7372,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7559,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7624,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7689,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7754,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7819,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7949,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +8014,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8079,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8144,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8209,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7886,7 +8274,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8339,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8465,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8782,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8847,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8912,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8977,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9103,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9168,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9233,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9298,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9363,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9428,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9493,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9167,7 +9619,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9684,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9810,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9411,7 +9875,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10062,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10127,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10192,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10318,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10383,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10448,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10021,7 +10513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10082,7 +10578,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10704,11 @@
           <t>76.213.681-3</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10769,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10834,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10899,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10964,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11029,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11094,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11159,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11407,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11472,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11537,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11602,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11732,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11241,7 +11797,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11302,7 +11862,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11927,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11424,7 +11992,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12057,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12122,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +12187,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12313,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12378,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12443,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12508,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11973,7 +12573,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12699,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12764,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12894,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12959,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +13024,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13089,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13154,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13280,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13345,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13410,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13475,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13540,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13605,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13918,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13983,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +14048,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14113,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13498,7 +14178,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14243,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14308,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14373,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14438,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14568,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14633,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14698,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14763,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14889,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14954,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +15019,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15084,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15149,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15214,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15279,11 @@
           <t>78.057.703-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15344,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15409,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15474,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15539,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15604,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15795,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15860,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15145,7 +15925,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15990,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +16055,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16120,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15389,7 +16185,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16250,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16315,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16380,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15633,7 +16445,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15694,7 +16510,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16575,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15816,7 +16640,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16705,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16831,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16896,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16961,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16243,7 +17087,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17152,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17217,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16426,7 +17282,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16487,7 +17347,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16548,7 +17412,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17477,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16670,7 +17542,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17607,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16792,7 +17672,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17737,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17802,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17867,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17932,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17997,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +18062,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17345,7 +18253,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17406,7 +18318,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17467,7 +18383,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17589,7 +18509,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17650,7 +18574,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17711,7 +18639,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17772,7 +18704,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17833,7 +18769,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17894,7 +18834,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18016,7 +18960,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18138,7 +19086,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18199,7 +19151,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18260,7 +19216,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18321,7 +19281,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18382,7 +19346,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18443,7 +19411,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18504,7 +19476,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18565,7 +19541,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18687,7 +19667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18809,7 +19793,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18931,7 +19919,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18992,7 +19984,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19053,7 +20049,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19114,7 +20114,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19175,7 +20179,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19236,7 +20244,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19297,7 +20309,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19358,7 +20374,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19419,7 +20439,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19602,7 +20626,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19663,7 +20691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19724,7 +20756,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19785,7 +20821,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19907,7 +20947,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19968,7 +21012,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20029,7 +21077,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20090,7 +21142,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20151,7 +21207,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20334,7 +21394,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20395,7 +21459,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20456,7 +21524,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20517,7 +21589,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20578,7 +21654,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20639,7 +21719,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +21784,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20761,7 +21849,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20883,7 +21975,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20944,7 +22040,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21005,7 +22105,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21066,7 +22170,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21127,7 +22235,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21188,7 +22300,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +22365,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21310,7 +22430,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +22556,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21493,7 +22621,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21554,7 +22686,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21676,7 +22812,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +22877,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21798,7 +22942,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21859,7 +23007,11 @@
           <t>77.786.423-8</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21920,7 +23072,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +23198,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +23263,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22164,7 +23328,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22225,7 +23393,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22286,7 +23458,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22347,7 +23523,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +23588,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22469,7 +23653,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22530,7 +23718,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +23783,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22652,7 +23848,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22774,7 +23974,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22835,7 +24039,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23022,7 +24230,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23083,7 +24295,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23144,7 +24360,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23205,7 +24425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23266,7 +24490,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23327,7 +24555,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23388,7 +24620,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23449,7 +24685,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23510,7 +24750,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23571,7 +24815,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23693,7 +24941,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23754,7 +25006,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23815,7 +25071,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23876,7 +25136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23937,7 +25201,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23998,7 +25266,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24059,7 +25331,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24120,7 +25396,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24181,7 +25461,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24242,7 +25526,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24303,7 +25591,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24364,7 +25656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24425,7 +25721,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24486,7 +25786,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24547,7 +25851,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24608,7 +25916,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24669,7 +25981,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24730,7 +26046,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24791,7 +26111,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24852,7 +26176,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24974,7 +26302,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25035,7 +26367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25096,7 +26432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25157,7 +26497,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25218,7 +26562,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25279,7 +26627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25340,7 +26692,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25401,7 +26757,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25462,7 +26822,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25523,7 +26887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25584,7 +26952,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25645,7 +27017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25706,7 +27082,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25767,7 +27147,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25828,7 +27212,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25889,7 +27277,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25950,7 +27342,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
@@ -1785,7 +1785,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3008,7 +3012,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3199,7 +3207,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4739,7 +4751,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6080,7 +6096,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10257,7 +10277,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12638,7 +12662,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13735,7 +13763,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15734,7 +15766,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19025,7 +19061,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19732,7 +19772,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20565,7 +20609,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21333,7 +21381,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22495,7 +22547,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23137,7 +23193,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24880,7 +24940,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M418"/>
+  <dimension ref="A1:M433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -969,7 +969,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1077908-15-CM25</t>
+          <t>1077908-14-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1009,32 +1009,28 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.751.057-8</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10526.67</v>
+        <v>2560.2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1077908-14-CM25</t>
+          <t>1077908-15-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1074,28 +1070,32 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MULTI SAFE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.751.057-8</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2560.2</v>
+        <v>10526.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>778989-4-CM25</t>
+          <t>2258-7846-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.081.190-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1135,17 +1135,17 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>3072.3</v>
+        <v>2091.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2258-7846-CM25</t>
+          <t>778989-4-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.081.190-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1200,17 +1200,17 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1219,7 +1219,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2091.34</v>
+        <v>3072.3</v>
       </c>
     </row>
     <row r="13">
@@ -1737,7 +1737,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1079454-38-CM25</t>
+          <t>1079454-40-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1796,13 +1796,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>4245.09</v>
+        <v>4134.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1079454-40-CM25</t>
+          <t>1079454-38-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1842,17 +1842,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1861,7 +1861,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4134.61</v>
+        <v>4245.09</v>
       </c>
     </row>
     <row r="23">
@@ -2062,7 +2062,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057385-69-CM25</t>
+          <t>3391-176-CM25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2102,17 +2102,17 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2121,13 +2121,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2927.42</v>
+        <v>3048.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3391-176-CM25</t>
+          <t>3391-177-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3048.69</v>
+        <v>8664.17</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>3391-177-CM25</t>
+          <t>1230848-16-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>70.954.900-6</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2232,17 +2232,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2251,13 +2251,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>8664.17</v>
+        <v>17537.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1230848-16-CM25</t>
+          <t>1230848-17-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2297,17 +2297,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2316,13 +2316,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17537.73</v>
+        <v>2205.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1230848-17-CM25</t>
+          <t>1057385-68-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2347,12 +2347,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.954.900-6</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Calama</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2205.11</v>
+        <v>3779.44</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1057385-68-CM25</t>
+          <t>1057385-69-CM25</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2446,7 +2446,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>3779.44</v>
+        <v>2927.42</v>
       </c>
     </row>
     <row r="32">
@@ -2517,7 +2517,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>769-4211-CM25</t>
+          <t>769-4216-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2572,13 +2572,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>11567.4</v>
+        <v>20611.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>769-4216-CM25</t>
+          <t>769-4211-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
+          <t>76.583.494-5</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>20611.39</v>
+        <v>11567.4</v>
       </c>
     </row>
     <row r="35">
@@ -2704,7 +2704,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>4051-55-CM25</t>
+          <t>1354-6-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.002.008-9</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2744,17 +2744,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2763,13 +2763,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4340.76</v>
+        <v>2649.64</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1354-6-CM25</t>
+          <t>4051-55-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.002.008-9</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2809,17 +2809,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2828,7 +2828,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2649.64</v>
+        <v>4340.76</v>
       </c>
     </row>
     <row r="38">
@@ -3029,7 +3029,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>930-36-CM25</t>
+          <t>930-37-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3088,13 +3088,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>2858.3</v>
+        <v>5906.22</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1220203-25-CM25</t>
+          <t>930-36-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3119,12 +3119,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3134,17 +3134,17 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3153,13 +3153,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3228.63</v>
+        <v>2858.3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>930-37-CM25</t>
+          <t>1220203-25-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3199,12 +3199,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>5906.22</v>
+        <v>3228.63</v>
       </c>
     </row>
     <row r="44">
@@ -3805,7 +3805,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>4291-269-CM25</t>
+          <t>4291-268-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3845,28 +3845,32 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>MULTI SAFE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.751.057-8</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>8923.75</v>
+        <v>10040.21</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>4291-268-CM25</t>
+          <t>4291-269-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3906,26 +3910,22 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.751.057-8</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>10040.21</v>
+        <v>8923.75</v>
       </c>
     </row>
     <row r="55">
@@ -3996,7 +3996,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1775-15-CM25</t>
+          <t>3916-184-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4021,12 +4021,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3227.3</v>
+        <v>3564.25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>3916-184-CM25</t>
+          <t>1775-15-CM25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3564.25</v>
+        <v>3227.3</v>
       </c>
     </row>
     <row r="58">
@@ -5857,7 +5857,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3916-251-CM25</t>
+          <t>2215-761-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5897,28 +5897,32 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>MULTI SAFE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.751.057-8</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>8025.31</v>
+        <v>47831.73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2215-761-CM25</t>
+          <t>3916-251-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5943,12 +5947,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -5958,26 +5962,22 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.751.057-8</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>47831.73</v>
+        <v>8025.31</v>
       </c>
     </row>
     <row r="87">
@@ -6503,7 +6503,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4291-869-CM25</t>
+          <t>2258-18359-CM25</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6523,17 +6523,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6562,13 +6562,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>18190.99</v>
+        <v>11546.03</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2258-18359-CM25</t>
+          <t>4291-869-CM25</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6588,17 +6588,17 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6627,7 +6627,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>11546.03</v>
+        <v>18190.99</v>
       </c>
     </row>
     <row r="97">
@@ -7344,7 +7344,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>1261592-3658-CM25</t>
+          <t>4999-118-CM25</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7384,32 +7384,28 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>MULTI SAFE SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.751.057-8</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>43684.36</v>
+        <v>15913.57</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>4999-118-CM25</t>
+          <t>1261592-3658-CM25</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7434,12 +7430,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7449,22 +7445,26 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>MULTI SAFE SPA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>76.751.057-8</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>15913.57</v>
+        <v>43684.36</v>
       </c>
     </row>
     <row r="110">
@@ -8949,7 +8949,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>3858-321-CM25</t>
+          <t>3858-320-CM25</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -8989,32 +8989,28 @@
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL COMPARO LIMITADA</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>76.290.943-K</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>15801.97</v>
+        <v>2453.99</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>3858-320-CM25</t>
+          <t>3858-321-CM25</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -9054,22 +9050,26 @@
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>COMERCIAL COMPARO LIMITADA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>76.290.943-K</t>
-        </is>
-      </c>
-      <c r="K134" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2453.99</v>
+        <v>15801.97</v>
       </c>
     </row>
     <row r="135">
@@ -9270,7 +9270,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>1057385-351-CM25</t>
+          <t>1113265-55-CM25</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9295,12 +9295,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>62.000.770-6</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9329,13 +9329,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2146.51</v>
+        <v>3380.32</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>650-79-CM25</t>
+          <t>1057385-351-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9360,12 +9360,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -9375,12 +9375,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
@@ -9394,13 +9394,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>3541.02</v>
+        <v>2146.51</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1113265-55-CM25</t>
+          <t>650-79-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>62.000.770-6</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA DE LA REGION DE ANTOFAGASTA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.213.681-3</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
@@ -9459,7 +9459,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3380.32</v>
+        <v>3541.02</v>
       </c>
     </row>
     <row r="141">
@@ -10294,7 +10294,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>4291-1685-CM25</t>
+          <t>1057384-666-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10353,13 +10353,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>2206.04</v>
+        <v>2855.44</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1057384-666-CM25</t>
+          <t>4291-1685-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10384,12 +10384,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10418,7 +10418,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>2855.44</v>
+        <v>2206.04</v>
       </c>
     </row>
     <row r="156">
@@ -11135,7 +11135,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2258-25783-CM25</t>
+          <t>769-4914-CM25</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11160,12 +11160,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -11175,32 +11175,28 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.774.294-0</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>53311.43</v>
+        <v>24860.83</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2258-25772-CM25</t>
+          <t>769-4917-CM25</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11225,12 +11221,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11240,12 +11236,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Barron Vieyra International Ltda.</t>
+          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>78.723.570-0</t>
+          <t>78.178.530-k</t>
         </is>
       </c>
       <c r="K168" t="inlineStr"/>
@@ -11255,13 +11251,13 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>28394.89</v>
+        <v>32863.67</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>769-4917-CM25</t>
+          <t>2258-25783-CM25</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11286,12 +11282,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11301,28 +11297,32 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>ROLAND VORWERK Y COMPANIA LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>78.178.530-k</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>32863.67</v>
+        <v>53311.43</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>769-4914-CM25</t>
+          <t>2258-25772-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11347,12 +11347,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  E INMOBILIARIA  FORBES  SPA</t>
+          <t>Barron Vieyra International Ltda.</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.774.294-0</t>
+          <t>78.723.570-0</t>
         </is>
       </c>
       <c r="K170" t="inlineStr"/>
@@ -11377,7 +11377,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>24860.83</v>
+        <v>28394.89</v>
       </c>
     </row>
     <row r="171">
@@ -13841,7 +13841,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1346284-21-CM26</t>
+          <t>1417-5-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13861,17 +13861,17 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13881,22 +13881,26 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>953.59</v>
+        <v>5432.52</v>
       </c>
     </row>
     <row r="210">
@@ -13967,7 +13971,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1417-5-CM26</t>
+          <t>1346284-21-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13987,17 +13991,17 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -14007,26 +14011,22 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
-        </is>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>5432.52</v>
+        <v>953.59</v>
       </c>
     </row>
     <row r="212">
@@ -14292,7 +14292,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>4291-127-CM26</t>
+          <t>881-8-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14351,13 +14351,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2320.5</v>
+        <v>9766.889999999999</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1357605-20-CM26</t>
+          <t>4291-127-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14377,17 +14377,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>71.186.200-5</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Corporación Cultural de Antofagasta</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14397,17 +14397,17 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
@@ -14416,13 +14416,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3863.62</v>
+        <v>2320.5</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>881-8-CM26</t>
+          <t>1357605-17-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14442,17 +14442,17 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>71.186.200-5</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>Corporación Cultural de Antofagasta</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -14462,17 +14462,17 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -14481,7 +14481,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>9766.889999999999</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="219">
@@ -14617,7 +14617,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1357605-17-CM26</t>
+          <t>1357605-20-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>2867</v>
+        <v>3863.62</v>
       </c>
     </row>
     <row r="222">
@@ -15133,7 +15133,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1775-7-CM26</t>
+          <t>3917-15-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15158,12 +15158,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15173,12 +15173,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JACKSON HOLE SPA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.057.703-7</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15192,13 +15192,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>3481.7</v>
+        <v>1304.76</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>3917-15-CM26</t>
+          <t>3917-17-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15257,13 +15257,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>1304.76</v>
+        <v>1737.06</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3917-17-CM26</t>
+          <t>1775-7-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15288,12 +15288,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>JACKSON HOLE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>78.057.703-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15322,13 +15322,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>1737.06</v>
+        <v>3481.7</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1171326-2-CM26</t>
+          <t>3391-99-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15353,12 +15353,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -15387,13 +15387,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2711.15</v>
+        <v>2026.51</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3858-62-CM26</t>
+          <t>3858-61-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15452,13 +15452,13 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>9948.209999999999</v>
+        <v>47093.88</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>3391-99-CM26</t>
+          <t>1171326-2-CM26</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -15483,12 +15483,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -15498,17 +15498,17 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
@@ -15517,13 +15517,13 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>2026.51</v>
+        <v>2711.15</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>3858-61-CM26</t>
+          <t>3858-62-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15582,7 +15582,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>47093.88</v>
+        <v>9948.209999999999</v>
       </c>
     </row>
     <row r="236">
@@ -15718,7 +15718,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1346284-26-CM26</t>
+          <t>3391-121-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15758,12 +15758,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -15777,13 +15777,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2839.83</v>
+        <v>876.61</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3391-121-CM26</t>
+          <t>1346284-26-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -15842,7 +15842,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>876.61</v>
+        <v>2839.83</v>
       </c>
     </row>
     <row r="240">
@@ -16043,7 +16043,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3917-25-CM26</t>
+          <t>3174-19-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16083,17 +16083,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16102,13 +16102,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1105.7</v>
+        <v>4585.72</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3174-19-CM26</t>
+          <t>3917-25-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16128,17 +16128,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16148,17 +16148,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -16167,7 +16167,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>4585.72</v>
+        <v>1105.7</v>
       </c>
     </row>
     <row r="245">
@@ -16238,7 +16238,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>558869-25-CM26</t>
+          <t>3858-80-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -16263,12 +16263,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -16278,17 +16278,17 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -16297,13 +16297,13 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>67305.96000000001</v>
+        <v>9482.67</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>3858-80-CM26</t>
+          <t>3858-82-CM26</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -16343,17 +16343,17 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -16362,13 +16362,13 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>9482.67</v>
+        <v>2199.64</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>3858-82-CM26</t>
+          <t>558869-25-CM26</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -16393,12 +16393,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -16408,17 +16408,17 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
@@ -16427,7 +16427,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>2199.64</v>
+        <v>67305.96000000001</v>
       </c>
     </row>
     <row r="249">
@@ -16563,7 +16563,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1057385-47-CM26</t>
+          <t>1057385-48-CM26</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16603,17 +16603,17 @@
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
@@ -16622,13 +16622,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>2516.7</v>
+        <v>2171.71</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1057385-48-CM26</t>
+          <t>1057385-47-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16668,17 +16668,17 @@
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L252" t="inlineStr">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2171.71</v>
+        <v>2516.7</v>
       </c>
     </row>
     <row r="253">
@@ -16884,7 +16884,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1233623-46-CM26</t>
+          <t>2385-126-CM26</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -16909,12 +16909,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.020.200-K</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE CALAMA</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -16924,26 +16924,22 @@
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2291.18</v>
+        <v>7705</v>
       </c>
     </row>
     <row r="257">
@@ -17014,7 +17010,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>2385-126-CM26</t>
+          <t>1233623-46-CM26</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17039,12 +17035,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>69.020.200-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALAMA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -17054,22 +17050,26 @@
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>7705</v>
+        <v>2291.18</v>
       </c>
     </row>
     <row r="259">
@@ -17465,7 +17465,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>4291-163-CM26</t>
+          <t>1233623-88-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17485,17 +17485,17 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17524,13 +17524,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>2777.7</v>
+        <v>10239.95</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1233623-88-CM26</t>
+          <t>1410-194-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17570,12 +17570,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17589,13 +17589,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>10239.95</v>
+        <v>1293.64</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1410-194-CM26</t>
+          <t>4291-163-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17615,17 +17615,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>1293.64</v>
+        <v>2777.7</v>
       </c>
     </row>
     <row r="268">
@@ -18497,7 +18497,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3858-122-CM26</t>
+          <t>3858-123-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18537,12 +18537,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2905.72</v>
+        <v>2368.88</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3858-123-CM26</t>
+          <t>3858-122-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18621,7 +18621,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2368.88</v>
+        <v>2905.72</v>
       </c>
     </row>
     <row r="283">
@@ -18692,7 +18692,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3858-126-CM26</t>
+          <t>3916-137-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18712,17 +18712,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18732,17 +18732,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18751,13 +18751,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4031.63</v>
+        <v>8531.57</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3916-137-CM26</t>
+          <t>3858-126-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18777,17 +18777,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18797,17 +18797,17 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>8531.57</v>
+        <v>4031.63</v>
       </c>
     </row>
     <row r="286">
@@ -18948,7 +18948,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>930-63-CM26</t>
+          <t>930-64-CM26</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -18988,12 +18988,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
@@ -19007,13 +19007,13 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>6671.33</v>
+        <v>2838.69</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>930-64-CM26</t>
+          <t>930-63-CM26</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -19053,12 +19053,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
@@ -19072,7 +19072,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2838.69</v>
+        <v>6671.33</v>
       </c>
     </row>
     <row r="290">
@@ -19143,7 +19143,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1694-5-CM26</t>
+          <t>1220203-23-CM26</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19163,17 +19163,17 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>60.803.000-k</t>
+          <t>60.905.047-0</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19202,13 +19202,13 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>2868.99</v>
+        <v>959.4400000000001</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1220203-23-CM26</t>
+          <t>1694-5-CM26</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -19228,17 +19228,17 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>60.905.047-0</t>
+          <t>60.803.000-k</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE IMPUESTOS INTERNOS DIRECCION</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -19267,13 +19267,13 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>959.4400000000001</v>
+        <v>2868.99</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>3391-222-CM26</t>
+          <t>2258-2707-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19298,12 +19298,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19332,13 +19332,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>1701.36</v>
+        <v>765.7</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3391-223-CM26</t>
+          <t>1233623-118-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19363,12 +19363,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19397,7 +19397,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1951.06</v>
+        <v>41354.92</v>
       </c>
     </row>
     <row r="295">
@@ -19468,7 +19468,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2258-2707-CM26</t>
+          <t>3391-223-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19493,12 +19493,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>765.7</v>
+        <v>1951.06</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1233623-118-CM26</t>
+          <t>3391-222-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19558,12 +19558,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19592,7 +19592,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>41354.92</v>
+        <v>1701.36</v>
       </c>
     </row>
     <row r="298">
@@ -19659,7 +19659,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3858-152-CM26</t>
+          <t>3858-153-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19699,12 +19699,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -19718,13 +19718,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2646.55</v>
+        <v>1206.46</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3858-153-CM26</t>
+          <t>3858-152-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19764,12 +19764,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -19783,7 +19783,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1206.46</v>
+        <v>2646.55</v>
       </c>
     </row>
     <row r="301">
@@ -19854,7 +19854,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2429-333-CM26</t>
+          <t>2429-346-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -19894,28 +19894,32 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>35542.28</v>
+        <v>25562.66</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2429-346-CM26</t>
+          <t>2429-333-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19935,7 +19939,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -19955,26 +19959,22 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr"/>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>25562.66</v>
+        <v>35542.28</v>
       </c>
     </row>
     <row r="304">
@@ -20435,7 +20435,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1261592-380-CM26</t>
+          <t>3391-269-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20460,12 +20460,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20494,13 +20494,13 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2424.13</v>
+        <v>1723.02</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1425773-37-CM26</t>
+          <t>1261592-380-CM26</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20520,17 +20520,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20540,28 +20540,32 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K312" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3765.92</v>
+        <v>2424.13</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1346284-88-CM26</t>
+          <t>1425773-37-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20581,17 +20585,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20601,32 +20605,28 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>4987.86</v>
+        <v>3765.92</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3391-269-CM26</t>
+          <t>1346284-88-CM26</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20651,12 +20651,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20666,12 +20666,12 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
@@ -20685,7 +20685,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>1723.02</v>
+        <v>4987.86</v>
       </c>
     </row>
     <row r="315">
@@ -20756,7 +20756,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1077908-73-CM26</t>
+          <t>2215-509-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20781,12 +20781,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20815,13 +20815,13 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>5039.81</v>
+        <v>21728.62</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>2215-509-CM26</t>
+          <t>1077908-73-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20846,12 +20846,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20880,7 +20880,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>21728.62</v>
+        <v>5039.81</v>
       </c>
     </row>
     <row r="318">
@@ -21077,7 +21077,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>3846-40-CM26</t>
+          <t>1233822-32-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21097,17 +21097,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21117,12 +21117,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -21136,7 +21136,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>5074.29</v>
+        <v>12053.09</v>
       </c>
     </row>
     <row r="322">
@@ -21207,7 +21207,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1233822-32-CM26</t>
+          <t>3846-40-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21227,17 +21227,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21247,12 +21247,12 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
@@ -21266,7 +21266,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>12053.09</v>
+        <v>5074.29</v>
       </c>
     </row>
     <row r="324">
@@ -21463,7 +21463,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3834-139-CM26</t>
+          <t>2258-4335-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21488,12 +21488,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21503,17 +21503,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21522,13 +21522,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4736.63</v>
+        <v>1151.17</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2258-4335-CM26</t>
+          <t>3834-139-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21553,12 +21553,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21568,17 +21568,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21587,7 +21587,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1151.17</v>
+        <v>4736.63</v>
       </c>
     </row>
     <row r="329">
@@ -22044,7 +22044,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1410-512-CM26</t>
+          <t>1057384-475-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22069,12 +22069,12 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22084,17 +22084,17 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
@@ -22103,13 +22103,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>830.96</v>
+        <v>6662.4</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1171326-33-CM26</t>
+          <t>4291-713-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22129,17 +22129,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -22168,13 +22168,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>3090.53</v>
+        <v>10823.9</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1057384-475-CM26</t>
+          <t>1171326-33-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22199,12 +22199,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22233,13 +22233,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>6662.4</v>
+        <v>3090.53</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>4291-713-CM26</t>
+          <t>1410-512-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22259,17 +22259,17 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -22279,17 +22279,17 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -22298,7 +22298,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>10823.9</v>
+        <v>830.96</v>
       </c>
     </row>
     <row r="340">
@@ -22434,7 +22434,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>697036-39-CM26</t>
+          <t>930-107-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22454,17 +22454,17 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22474,12 +22474,12 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
@@ -22493,13 +22493,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>810.01</v>
+        <v>5139.73</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>930-107-CM26</t>
+          <t>697036-39-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22519,17 +22519,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22539,12 +22539,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -22558,7 +22558,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>5139.73</v>
+        <v>810.01</v>
       </c>
     </row>
     <row r="344">
@@ -22885,7 +22885,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>2258-5341-CM26</t>
+          <t>1410-553-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22910,12 +22910,12 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22925,12 +22925,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -22944,13 +22944,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>781</v>
+        <v>789.45</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1410-553-CM26</t>
+          <t>2258-5341-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22975,12 +22975,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22990,12 +22990,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -23009,13 +23009,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>789.45</v>
+        <v>781</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>769-438-CM26</t>
+          <t>2258-5351-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23040,12 +23040,12 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -23055,12 +23055,12 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>ACC INVERSIONES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>77.786.423-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K351" t="inlineStr">
@@ -23074,13 +23074,13 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>20759.6</v>
+        <v>24827.51</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>2258-5351-CM26</t>
+          <t>769-438-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23105,12 +23105,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ACC INVERSIONES SPA</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.786.423-8</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>24827.51</v>
+        <v>20759.6</v>
       </c>
     </row>
     <row r="353">
@@ -23340,7 +23340,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2429-769-CM26</t>
+          <t>2122-136-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23365,12 +23365,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23399,13 +23399,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>26618.46</v>
+        <v>3346.09</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2122-136-CM26</t>
+          <t>2429-769-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -23430,12 +23430,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -23464,13 +23464,13 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>3346.09</v>
+        <v>26618.46</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>2215-753-CM26</t>
+          <t>1077908-128-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23495,12 +23495,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>15324.27</v>
+        <v>11449.09</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1077908-128-CM26</t>
+          <t>2215-753-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23560,12 +23560,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>11449.09</v>
+        <v>15324.27</v>
       </c>
     </row>
     <row r="360">
@@ -23730,7 +23730,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1077908-127-CM26</t>
+          <t>4291-961-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23750,17 +23750,17 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23770,12 +23770,12 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
@@ -23789,13 +23789,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>4055.74</v>
+        <v>2422.51</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>4291-961-CM26</t>
+          <t>1077908-127-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23815,17 +23815,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23835,12 +23835,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -23854,7 +23854,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2422.51</v>
+        <v>4055.74</v>
       </c>
     </row>
     <row r="364">
@@ -24242,7 +24242,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>4999-25-CM26</t>
+          <t>3858-321-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24267,12 +24267,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24282,17 +24282,17 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
@@ -24301,13 +24301,13 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>8216.299999999999</v>
+        <v>4988.22</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>4999-26-CM26</t>
+          <t>2215-807-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24332,12 +24332,12 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>69.252.500-0</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24347,17 +24347,17 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -24366,13 +24366,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2091.06</v>
+        <v>45781.56</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>2215-807-CM26</t>
+          <t>4999-26-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -24397,12 +24397,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -24412,17 +24412,17 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
@@ -24431,13 +24431,13 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>45781.56</v>
+        <v>2091.06</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>3858-321-CM26</t>
+          <t>4999-25-CM26</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -24462,12 +24462,12 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.252.500-0</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -24477,17 +24477,17 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
@@ -24496,7 +24496,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>4988.22</v>
+        <v>8216.299999999999</v>
       </c>
     </row>
     <row r="374">
@@ -24567,7 +24567,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1261592-897-CM26</t>
+          <t>3246-294-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24587,17 +24587,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.103.019-3</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24607,17 +24607,17 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -24626,13 +24626,13 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>878.5700000000001</v>
+        <v>1057.45</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1261592-896-CM26</t>
+          <t>1261592-897-CM26</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -24672,17 +24672,17 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L376" t="inlineStr">
@@ -24691,13 +24691,13 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>6730.82</v>
+        <v>878.5700000000001</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1233623-372-CM26</t>
+          <t>1261592-896-CM26</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -24717,17 +24717,17 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G377" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H377" t="inlineStr">
@@ -24737,17 +24737,17 @@
       </c>
       <c r="I377" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L377" t="inlineStr">
@@ -24756,13 +24756,13 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>2323.84</v>
+        <v>6730.82</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1233623-369-CM26</t>
+          <t>1233623-372-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24821,13 +24821,13 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>8181.57</v>
+        <v>2323.84</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>3246-294-CM26</t>
+          <t>1233623-369-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24852,12 +24852,12 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>61.103.019-3</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -24867,12 +24867,12 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K379" t="inlineStr">
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>1057.45</v>
+        <v>8181.57</v>
       </c>
     </row>
     <row r="380">
@@ -25152,7 +25152,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>4291-994-CM26</t>
+          <t>1233623-416-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25177,12 +25177,12 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G384" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H384" t="inlineStr">
@@ -25211,13 +25211,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>2864.54</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1233623-416-CM26</t>
+          <t>3391-508-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25237,17 +25237,17 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25257,17 +25257,17 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -25276,13 +25276,13 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>5053.31</v>
+        <v>9726.92</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>3391-508-CM26</t>
+          <t>4291-994-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25302,17 +25302,17 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25322,17 +25322,17 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -25341,7 +25341,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>9726.92</v>
+        <v>2864.54</v>
       </c>
     </row>
     <row r="387">
@@ -25477,7 +25477,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3845-56-CM26</t>
+          <t>3858-361-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25502,12 +25502,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25517,17 +25517,17 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -25536,13 +25536,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>3956.86</v>
+        <v>977.65</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3858-361-CM26</t>
+          <t>3845-56-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25567,12 +25567,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25582,17 +25582,17 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25601,7 +25601,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>977.65</v>
+        <v>3956.86</v>
       </c>
     </row>
     <row r="391">
@@ -25672,7 +25672,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1233623-486-CM26</t>
+          <t>4051-169-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25697,12 +25697,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25712,12 +25712,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  JMK  SPA</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.700.129-9</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -25731,13 +25731,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>2885.37</v>
+        <v>805.98</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>4051-169-CM26</t>
+          <t>1233623-486-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25762,12 +25762,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25777,12 +25777,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  JMK  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>77.700.129-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25796,7 +25796,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>805.98</v>
+        <v>2885.37</v>
       </c>
     </row>
     <row r="394">
@@ -25867,7 +25867,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>2258-6534-CM26</t>
+          <t>769-587-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25892,12 +25892,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25907,17 +25907,17 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L395" t="inlineStr">
@@ -25926,13 +25926,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>25156.69</v>
+        <v>23360.65</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>769-587-CM26</t>
+          <t>2258-6534-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25957,12 +25957,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25972,17 +25972,17 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -25991,7 +25991,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>23360.65</v>
+        <v>25156.69</v>
       </c>
     </row>
     <row r="397">
@@ -26513,7 +26513,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1057384-746-CM26</t>
+          <t>1261592-1139-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26553,17 +26553,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26572,13 +26572,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>5918.89</v>
+        <v>39511.4</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1261592-1139-CM26</t>
+          <t>1057384-746-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26603,12 +26603,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26618,17 +26618,17 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -26637,13 +26637,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>39511.4</v>
+        <v>5918.89</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1233623-604-CM26</t>
+          <t>993-211-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26668,12 +26668,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26702,13 +26702,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>2656.73</v>
+        <v>1065.36</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>993-211-CM26</t>
+          <t>1233623-604-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26728,17 +26728,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26767,7 +26767,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1065.36</v>
+        <v>2656.73</v>
       </c>
     </row>
     <row r="409">
@@ -26838,7 +26838,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1057385-339-CM26</t>
+          <t>1057385-344-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26878,17 +26878,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -26897,13 +26897,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>2376.26</v>
+        <v>1629.03</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1057385-344-CM26</t>
+          <t>1057385-339-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26943,17 +26943,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -26962,13 +26962,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>1629.03</v>
+        <v>2376.26</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>650-113-CM26</t>
+          <t>697036-67-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26993,12 +26993,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27027,13 +27027,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2630.04</v>
+        <v>2799.45</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>697036-67-CM26</t>
+          <t>650-113-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27058,12 +27058,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27092,7 +27092,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2799.45</v>
+        <v>2630.04</v>
       </c>
     </row>
     <row r="414">
@@ -27378,7 +27378,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -27418,6 +27418,969 @@
       </c>
       <c r="M418" s="2" t="n">
         <v>829.79</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>2215-1097-CM26</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>61.606.202-6</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="n">
+        <v>26282.88</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>2215-1062-CM26</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>61.606.202-6</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>GRUPO DK SERVICIOS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>76.556.184-1</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="n">
+        <v>3658.34</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>2215-1055-CM26</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>61.606.202-6</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>DIFEM LABORATORIOS S A</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>79.581.120-6</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M421" s="2" t="n">
+        <v>6456.54</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>1233623-786-CM26</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>61.980.920-3</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Licancabur</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="n">
+        <v>3476.82</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>769-710-CM26</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>JIREH SOLUTION SPA</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>78.061.716-0</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="n">
+        <v>27337.12</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>1171326-56-CM26</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>61.926.300-6</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="n">
+        <v>1962.84</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>3846-72-CM26</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>69.253.200-7</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="n">
+        <v>1246.54</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>1261592-1284-CM26</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>71.102.600-2</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="n">
+        <v>339103.42</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>2258-7681-CM26</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="n">
+        <v>21187.19</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>3149-315-CM26</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>69.253.600-2</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Francisco javier</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>76.882.403-7</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M428" s="2" t="n">
+        <v>73075.14999999999</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>2258-8173-CM26</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Barron Vieyra International Ltda.</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M429" s="2" t="n">
+        <v>5138.71</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>4291-1714-CM26</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="n">
+        <v>18639.61</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>769-757-CM26</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>61.606.200-k</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>ACC INVERSIONES SPA</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>77.786.423-8</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="n">
+        <v>14857.02</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2258-7840-CM26</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>61.606.201-8</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M432" s="2" t="n">
+        <v>1526.7</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>1346284-213-CM26</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>62.000.970-9</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>1563.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M433"/>
+  <dimension ref="A1:M434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -13861,7 +13861,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -14422,7 +14422,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1357605-17-CM26</t>
+          <t>1357605-20-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14481,13 +14481,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2867</v>
+        <v>3863.62</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>881-6-CM26</t>
+          <t>1357605-17-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14507,17 +14507,17 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>71.186.200-5</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>Corporación Cultural de Antofagasta</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14527,17 +14527,17 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -14546,13 +14546,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>842.62</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>881-2-CM26</t>
+          <t>881-6-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14592,17 +14592,17 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>COMERCIAL BAUSTORE SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>77.621.112-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -14611,13 +14611,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>1204.97</v>
+        <v>842.62</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1357605-20-CM26</t>
+          <t>881-2-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14637,17 +14637,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>71.186.200-5</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Corporación Cultural de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14657,17 +14657,17 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>COMERCIAL BAUSTORE SPA</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>77.621.112-5</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -14676,7 +14676,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>3863.62</v>
+        <v>1204.97</v>
       </c>
     </row>
     <row r="222">
@@ -14812,7 +14812,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1077908-23-CM26</t>
+          <t>1077908-24-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14852,28 +14852,32 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K224" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2414.23</v>
+        <v>5758.8</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1077908-24-CM26</t>
+          <t>1077908-25-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14913,17 +14917,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14932,13 +14936,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>5758.8</v>
+        <v>3105.16</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1077908-25-CM26</t>
+          <t>1077908-23-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14978,26 +14982,22 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>3105.16</v>
+        <v>2414.23</v>
       </c>
     </row>
     <row r="227">
@@ -15133,7 +15133,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>3917-15-CM26</t>
+          <t>1775-7-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15158,12 +15158,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>60.804.004-8</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15173,12 +15173,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>JACKSON HOLE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>78.057.703-7</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1304.76</v>
+        <v>3481.7</v>
       </c>
     </row>
     <row r="230">
@@ -15263,7 +15263,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1775-7-CM26</t>
+          <t>3917-15-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15288,12 +15288,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>60.804.004-8</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15303,12 +15303,12 @@
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JACKSON HOLE SPA</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.057.703-7</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15322,7 +15322,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3481.7</v>
+        <v>1304.76</v>
       </c>
     </row>
     <row r="232">
@@ -15718,7 +15718,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3391-121-CM26</t>
+          <t>1346284-26-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15758,12 +15758,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -15777,13 +15777,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>876.61</v>
+        <v>2839.83</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1346284-26-CM26</t>
+          <t>3391-121-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -15842,7 +15842,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2839.83</v>
+        <v>876.61</v>
       </c>
     </row>
     <row r="240">
@@ -16043,7 +16043,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>3174-19-CM26</t>
+          <t>3917-25-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -16063,17 +16063,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -16083,17 +16083,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -16102,13 +16102,13 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>4585.72</v>
+        <v>1105.7</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>3917-25-CM26</t>
+          <t>3174-19-CM26</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -16133,12 +16133,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -16148,17 +16148,17 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -16167,7 +16167,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>1105.7</v>
+        <v>4585.72</v>
       </c>
     </row>
     <row r="245">
@@ -17335,7 +17335,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>769-129-CM26</t>
+          <t>769-133-CM26</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -17375,12 +17375,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>COMERCIALIZADORA MALUSANT SPA</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>77.720.988-4</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
@@ -17394,13 +17394,13 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>37361.19</v>
+        <v>26220.01</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>769-133-CM26</t>
+          <t>769-129-CM26</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -17440,12 +17440,12 @@
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA MALUSANT SPA</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>77.720.988-4</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -17459,13 +17459,13 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>26220.01</v>
+        <v>37361.19</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1233623-88-CM26</t>
+          <t>1410-194-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17490,12 +17490,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17524,13 +17524,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>10239.95</v>
+        <v>1293.64</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1410-194-CM26</t>
+          <t>1233623-88-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17570,12 +17570,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17589,7 +17589,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>1293.64</v>
+        <v>10239.95</v>
       </c>
     </row>
     <row r="267">
@@ -17790,7 +17790,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1079454-63-CM26</t>
+          <t>3917-33-CM26</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -17815,12 +17815,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -17830,17 +17830,17 @@
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -17849,7 +17849,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>1136.05</v>
+        <v>1311.13</v>
       </c>
     </row>
     <row r="271">
@@ -17920,7 +17920,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>3917-33-CM26</t>
+          <t>1079454-63-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17945,12 +17945,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17960,17 +17960,17 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>1311.13</v>
+        <v>1136.05</v>
       </c>
     </row>
     <row r="273">
@@ -18115,7 +18115,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>881-43-CM26</t>
+          <t>558869-41-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18135,17 +18135,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18155,28 +18155,32 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.478.731-5</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
+          <t>76.213.681-3</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>3944.99</v>
+        <v>139.6</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>558869-41-CM26</t>
+          <t>881-43-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18196,17 +18200,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18216,26 +18220,22 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES DEL NORTE S.A.</t>
+          <t>SERVICIOS,  DISTRIBUCION Y LOGÍSTICA BRICH LIMITADA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>76.213.681-3</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
+          <t>76.478.731-5</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>139.6</v>
+        <v>3944.99</v>
       </c>
     </row>
     <row r="277">
@@ -18306,7 +18306,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1057384-229-CM26</t>
+          <t>697036-14-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18326,17 +18326,17 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18365,13 +18365,13 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1733.21</v>
+        <v>795.53</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1604-15-CM26</t>
+          <t>4468-28-CM26</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -18396,12 +18396,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>60.511.020-7</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -18411,32 +18411,28 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>859.96</v>
+        <v>35118.49</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>4468-28-CM26</t>
+          <t>1604-15-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18461,12 +18457,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>60.511.020-7</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18476,28 +18472,32 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K280" t="inlineStr"/>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>35118.49</v>
+        <v>859.96</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>3858-123-CM26</t>
+          <t>1057384-229-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18517,17 +18517,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18537,12 +18537,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>2368.88</v>
+        <v>1733.21</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3858-122-CM26</t>
+          <t>3858-123-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18621,13 +18621,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2905.72</v>
+        <v>2368.88</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>697036-14-CM26</t>
+          <t>3858-122-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18652,12 +18652,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18686,13 +18686,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>795.53</v>
+        <v>2905.72</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3916-137-CM26</t>
+          <t>3858-126-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18712,17 +18712,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18732,17 +18732,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18751,13 +18751,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>8531.57</v>
+        <v>4031.63</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3858-126-CM26</t>
+          <t>3916-137-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18777,17 +18777,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18797,17 +18797,17 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4031.63</v>
+        <v>8531.57</v>
       </c>
     </row>
     <row r="286">
@@ -19273,7 +19273,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>2258-2707-CM26</t>
+          <t>1233623-116-CM26</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -19298,12 +19298,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -19332,13 +19332,13 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>765.7</v>
+        <v>51693.65</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1233623-118-CM26</t>
+          <t>3391-223-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19363,12 +19363,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -19397,13 +19397,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>41354.92</v>
+        <v>1951.06</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1233623-116-CM26</t>
+          <t>3391-222-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19428,12 +19428,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19462,13 +19462,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>51693.65</v>
+        <v>1701.36</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>3391-223-CM26</t>
+          <t>2258-2707-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19493,12 +19493,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>1951.06</v>
+        <v>765.7</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>3391-222-CM26</t>
+          <t>1233623-118-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19558,12 +19558,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19592,7 +19592,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>1701.36</v>
+        <v>41354.92</v>
       </c>
     </row>
     <row r="298">
@@ -19659,7 +19659,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>3858-153-CM26</t>
+          <t>3858-152-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19699,12 +19699,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
@@ -19718,13 +19718,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1206.46</v>
+        <v>2646.55</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>3858-152-CM26</t>
+          <t>3858-153-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19764,12 +19764,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
@@ -19783,7 +19783,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>2646.55</v>
+        <v>1206.46</v>
       </c>
     </row>
     <row r="301">
@@ -20045,7 +20045,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1233623-128-CM26</t>
+          <t>1057384-328-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20065,17 +20065,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20104,13 +20104,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>13901.14</v>
+        <v>6142.49</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1057384-328-CM26</t>
+          <t>1233623-128-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20130,17 +20130,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20169,13 +20169,13 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>6142.49</v>
+        <v>13901.14</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>707415-53-CM26</t>
+          <t>2429-374-CM26</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -20195,17 +20195,17 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -20234,13 +20234,13 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>28505.77</v>
+        <v>3871.87</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>2429-374-CM26</t>
+          <t>707415-53-CM26</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -20260,17 +20260,17 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -20299,7 +20299,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>3871.87</v>
+        <v>28505.77</v>
       </c>
     </row>
     <row r="309">
@@ -20435,7 +20435,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>3391-269-CM26</t>
+          <t>1425773-37-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20455,17 +20455,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20475,26 +20475,22 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr"/>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>1723.02</v>
+        <v>3765.92</v>
       </c>
     </row>
     <row r="312">
@@ -20565,7 +20561,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1425773-37-CM26</t>
+          <t>3391-269-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20585,17 +20581,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20605,22 +20601,26 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3765.92</v>
+        <v>1723.02</v>
       </c>
     </row>
     <row r="314">
@@ -20756,7 +20756,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2215-509-CM26</t>
+          <t>2258-3578-CM26</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20781,12 +20781,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20796,32 +20796,28 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>Barron Vieyra International Ltda.</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
-        </is>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>Coquimbo</t>
-        </is>
-      </c>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr"/>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>21728.62</v>
+        <v>7440.4</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1077908-73-CM26</t>
+          <t>2215-509-CM26</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -20846,12 +20842,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -20880,13 +20876,13 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>5039.81</v>
+        <v>21728.62</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>2258-3578-CM26</t>
+          <t>1077908-73-CM26</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -20911,12 +20907,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20926,22 +20922,26 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Barron Vieyra International Ltda.</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>78.723.570-0</t>
-        </is>
-      </c>
-      <c r="K318" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>7440.4</v>
+        <v>5039.81</v>
       </c>
     </row>
     <row r="319">
@@ -21077,7 +21077,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>1233822-32-CM26</t>
+          <t>4291-473-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21097,17 +21097,17 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>65.076.481-1</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21117,12 +21117,12 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
@@ -21136,13 +21136,13 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>12053.09</v>
+        <v>4970.25</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>4291-473-CM26</t>
+          <t>1233822-32-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -21162,17 +21162,17 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>65.076.481-1</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CORPORACION MUNICIPAL DE DEPORTES Y RECREACIÓN DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -21182,12 +21182,12 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
@@ -21201,7 +21201,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>4970.25</v>
+        <v>12053.09</v>
       </c>
     </row>
     <row r="323">
@@ -21463,7 +21463,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>2258-4335-CM26</t>
+          <t>3834-139-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21488,12 +21488,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21503,17 +21503,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21522,13 +21522,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>1151.17</v>
+        <v>4736.63</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>3834-139-CM26</t>
+          <t>2258-4335-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21553,12 +21553,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21568,17 +21568,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21587,7 +21587,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>4736.63</v>
+        <v>1151.17</v>
       </c>
     </row>
     <row r="329">
@@ -21723,7 +21723,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1057385-159-CM26</t>
+          <t>1499684-25-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21743,17 +21743,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>65.077.905-3</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>FUNDACION DE CULTURA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21763,17 +21763,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21782,7 +21782,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>844.88</v>
+        <v>941.3</v>
       </c>
     </row>
     <row r="332">
@@ -21853,7 +21853,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2215-672-CM26</t>
+          <t>1057385-159-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21868,7 +21868,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -21878,12 +21878,12 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21893,17 +21893,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21912,13 +21912,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>33243.42</v>
+        <v>844.88</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>3149-160-CM26</t>
+          <t>2215-672-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21933,22 +21933,22 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21958,28 +21958,32 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K334" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>16983.97</v>
+        <v>33243.42</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1079454-221-CM26</t>
+          <t>3149-160-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -21994,7 +21998,7 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
@@ -22004,12 +22008,12 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22019,32 +22023,28 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K335" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr"/>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>877.37</v>
+        <v>16983.97</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1057384-475-CM26</t>
+          <t>1079454-221-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22059,22 +22059,22 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -22103,13 +22103,13 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>6662.4</v>
+        <v>877.37</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>4291-713-CM26</t>
+          <t>1057384-475-CM26</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -22129,17 +22129,17 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -22149,12 +22149,12 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
@@ -22168,13 +22168,13 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>10823.9</v>
+        <v>6662.4</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1171326-33-CM26</t>
+          <t>4291-713-CM26</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -22194,17 +22194,17 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -22214,12 +22214,12 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
@@ -22233,13 +22233,13 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3090.53</v>
+        <v>10823.9</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1410-512-CM26</t>
+          <t>1171326-33-CM26</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -22264,7 +22264,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -22279,17 +22279,17 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
@@ -22298,13 +22298,13 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>830.96</v>
+        <v>3090.53</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1079454-226-CM26</t>
+          <t>1410-512-CM26</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -22319,22 +22319,22 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -22344,17 +22344,17 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
@@ -22363,13 +22363,13 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>1783.74</v>
+        <v>830.96</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>838098-26-CM26</t>
+          <t>1079454-226-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22394,12 +22394,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>73.923.800-5</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22409,17 +22409,17 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
@@ -22428,13 +22428,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>949.58</v>
+        <v>1783.74</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>930-107-CM26</t>
+          <t>838098-25-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22449,7 +22449,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
@@ -22459,12 +22459,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>73.923.800-5</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22474,17 +22474,17 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
@@ -22493,13 +22493,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>5139.73</v>
+        <v>1150.67</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>697036-39-CM26</t>
+          <t>930-107-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22519,17 +22519,17 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -22539,12 +22539,12 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
@@ -22558,13 +22558,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>810.01</v>
+        <v>5139.73</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>697036-40-CM26</t>
+          <t>697036-39-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22579,7 +22579,7 @@
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
@@ -22623,13 +22623,13 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>4487.52</v>
+        <v>810.01</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>3858-275-CM26</t>
+          <t>697036-40-CM26</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -22654,12 +22654,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -22688,13 +22688,13 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>12010.24</v>
+        <v>4487.52</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1375735-23-CM26</t>
+          <t>3858-275-CM26</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -22709,22 +22709,22 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>61.981.250-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -22734,17 +22734,17 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
@@ -22753,13 +22753,13 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>7161.54</v>
+        <v>12010.24</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>3506-448-CM26</t>
+          <t>1375735-23-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22779,17 +22779,17 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.981.250-6</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22799,28 +22799,32 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>Equilibrium SpA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>76.475.342-9</t>
-        </is>
-      </c>
-      <c r="K347" t="inlineStr"/>
+          <t>77.012.870-6</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>2428.37</v>
+        <v>7161.54</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>3858-279-CM26</t>
+          <t>3506-448-CM26</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -22835,7 +22839,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -22845,12 +22849,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -22860,32 +22864,28 @@
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>Equilibrium SpA</t>
         </is>
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.475.342-9</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr"/>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>911.9</v>
+        <v>2428.37</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1410-553-CM26</t>
+          <t>3858-279-CM26</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -22900,22 +22900,22 @@
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -22925,12 +22925,12 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K349" t="inlineStr">
@@ -22944,13 +22944,13 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>789.45</v>
+        <v>911.9</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>2258-5341-CM26</t>
+          <t>1410-553-CM26</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -22975,12 +22975,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -22990,12 +22990,12 @@
       </c>
       <c r="I350" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K350" t="inlineStr">
@@ -23009,13 +23009,13 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>781</v>
+        <v>789.45</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>2258-5351-CM26</t>
+          <t>2258-5341-CM26</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -23030,7 +23030,7 @@
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
@@ -23074,7 +23074,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>24827.51</v>
+        <v>781</v>
       </c>
     </row>
     <row r="352">
@@ -23145,7 +23145,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1346284-115-CM26</t>
+          <t>2258-5351-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23160,7 +23160,7 @@
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
@@ -23170,12 +23170,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23185,12 +23185,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -23204,13 +23204,13 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>924.59</v>
+        <v>24827.51</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1233623-340-CM26</t>
+          <t>1346284-115-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -23220,27 +23220,27 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -23250,12 +23250,12 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K354" t="inlineStr">
@@ -23269,13 +23269,13 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>5179.97</v>
+        <v>924.59</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1057385-189-CM26</t>
+          <t>1233623-340-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -23290,22 +23290,22 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -23334,13 +23334,13 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3340.58</v>
+        <v>5179.97</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>2122-136-CM26</t>
+          <t>1057385-189-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -23355,7 +23355,7 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
@@ -23365,12 +23365,12 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -23380,17 +23380,17 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L356" t="inlineStr">
@@ -23399,7 +23399,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>3346.09</v>
+        <v>3340.58</v>
       </c>
     </row>
     <row r="357">
@@ -23470,7 +23470,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1077908-128-CM26</t>
+          <t>2122-136-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
@@ -23495,12 +23495,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -23510,17 +23510,17 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
@@ -23529,13 +23529,13 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>11449.09</v>
+        <v>3346.09</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>2215-753-CM26</t>
+          <t>1077908-128-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -23560,12 +23560,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -23594,7 +23594,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>15324.27</v>
+        <v>11449.09</v>
       </c>
     </row>
     <row r="360">
@@ -23665,7 +23665,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>3174-137-CM26</t>
+          <t>2215-753-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23680,7 +23680,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -23690,12 +23690,12 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.102.045-7</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23705,17 +23705,17 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
@@ -23724,13 +23724,13 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1391.12</v>
+        <v>15324.27</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>4291-961-CM26</t>
+          <t>3174-137-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23745,22 +23745,22 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.102.045-7</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23789,13 +23789,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>2422.51</v>
+        <v>1391.12</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1077908-127-CM26</t>
+          <t>4291-961-CM26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -23815,17 +23815,17 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>62.000.380-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>CENTRO ONCOLOGICO DEL NORTE</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23835,12 +23835,12 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>AVA COMERCIAL SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>78.203.286-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
@@ -23854,13 +23854,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>4055.74</v>
+        <v>2422.51</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>4291-972-CM26</t>
+          <t>1077908-127-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23875,22 +23875,22 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>62.000.380-8</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>CENTRO ONCOLOGICO DEL NORTE</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -23900,12 +23900,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>AVA COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.203.286-0</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
@@ -23919,13 +23919,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>10760.91</v>
+        <v>4055.74</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2258-5683-CM26</t>
+          <t>4291-972-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23945,17 +23945,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23965,28 +23965,32 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Barron Vieyra International Ltda.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>78.723.570-0</t>
-        </is>
-      </c>
-      <c r="K365" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>11040.08</v>
+        <v>10760.91</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>3834-219-CM26</t>
+          <t>2258-5683-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24001,7 +24005,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -24011,12 +24015,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24026,32 +24030,28 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Barron Vieyra International Ltda.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K366" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>1234.63</v>
+        <v>11040.08</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1057385-208-CM26</t>
+          <t>3834-219-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24066,7 +24066,7 @@
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -24076,12 +24076,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24110,13 +24110,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>1086</v>
+        <v>1234.63</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>707415-77-CM26</t>
+          <t>1057385-208-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24131,22 +24131,22 @@
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24175,13 +24175,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>108430.38</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1057385-214-CM26</t>
+          <t>707415-77-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24221,28 +24221,32 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>prodesa</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>96.828.760-5</t>
-        </is>
-      </c>
-      <c r="K369" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>1070.74</v>
+        <v>108430.38</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>3858-321-CM26</t>
+          <t>1057385-214-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24257,22 +24261,22 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24282,26 +24286,22 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>prodesa</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.828.760-5</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr"/>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>4988.22</v>
+        <v>1070.74</v>
       </c>
     </row>
     <row r="371">
@@ -24502,7 +24502,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1261592-889-CM26</t>
+          <t>3858-321-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24517,22 +24517,22 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24542,12 +24542,12 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>PROVEEDORA KENUA SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>78.212.867-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
@@ -24561,13 +24561,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>8846.809999999999</v>
+        <v>4988.22</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>3246-294-CM26</t>
+          <t>1261592-889-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -24582,22 +24582,22 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>61.103.019-3</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -24607,12 +24607,12 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>PROVEEDORA KENUA SPA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>78.212.867-1</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
@@ -24626,7 +24626,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>1057.45</v>
+        <v>8846.809999999999</v>
       </c>
     </row>
     <row r="376">
@@ -24892,7 +24892,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1346284-128-CM26</t>
+          <t>3246-294-CM26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -24907,22 +24907,22 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.103.019-3</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -24932,12 +24932,12 @@
       </c>
       <c r="I380" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K380" t="inlineStr">
@@ -24951,13 +24951,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>12579.75</v>
+        <v>1057.45</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>3391-484-CM26</t>
+          <t>1346284-128-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -24972,22 +24972,22 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -24997,17 +24997,17 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L381" t="inlineStr">
@@ -25016,13 +25016,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>1653.63</v>
+        <v>12579.75</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1233623-354-CM26</t>
+          <t>3391-484-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25037,22 +25037,22 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25062,17 +25062,17 @@
       </c>
       <c r="I382" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L382" t="inlineStr">
@@ -25081,13 +25081,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>794.3</v>
+        <v>1653.63</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1233623-355-CM26</t>
+          <t>1233623-416-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25146,13 +25146,13 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>866.74</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1233623-416-CM26</t>
+          <t>1233623-355-CM26</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -25211,13 +25211,13 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>5053.31</v>
+        <v>866.74</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>3391-508-CM26</t>
+          <t>1233623-354-CM26</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -25242,12 +25242,12 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G385" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H385" t="inlineStr">
@@ -25257,17 +25257,17 @@
       </c>
       <c r="I385" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L385" t="inlineStr">
@@ -25276,7 +25276,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>9726.92</v>
+        <v>794.3</v>
       </c>
     </row>
     <row r="386">
@@ -25347,7 +25347,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1079454-361-CM26</t>
+          <t>3391-508-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25357,27 +25357,27 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25387,17 +25387,17 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -25406,7 +25406,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>1117.66</v>
+        <v>9726.92</v>
       </c>
     </row>
     <row r="388">
@@ -25477,7 +25477,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>3858-361-CM26</t>
+          <t>1079454-361-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25492,7 +25492,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -25502,12 +25502,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25517,17 +25517,17 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -25536,13 +25536,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>977.65</v>
+        <v>1117.66</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>3845-56-CM26</t>
+          <t>3858-361-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25567,12 +25567,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25582,17 +25582,17 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L390" t="inlineStr">
@@ -25601,13 +25601,13 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>3956.86</v>
+        <v>977.65</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1233623-508-CM26</t>
+          <t>3845-56-CM26</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -25622,7 +25622,7 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -25632,12 +25632,12 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G391" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H391" t="inlineStr">
@@ -25647,17 +25647,17 @@
       </c>
       <c r="I391" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L391" t="inlineStr">
@@ -25666,13 +25666,13 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>1766.5</v>
+        <v>3956.86</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>4051-169-CM26</t>
+          <t>1233623-508-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -25687,7 +25687,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -25697,12 +25697,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>69.252.600-7</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OLLAGUE</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25712,12 +25712,12 @@
       </c>
       <c r="I392" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA  JMK  SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>77.700.129-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K392" t="inlineStr">
@@ -25731,13 +25731,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>805.98</v>
+        <v>1766.5</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1233623-486-CM26</t>
+          <t>4051-169-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25762,12 +25762,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>69.252.600-7</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>I MUNICIPALIDAD DE OLLAGUE</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25777,12 +25777,12 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA  JMK  SPA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.700.129-9</t>
         </is>
       </c>
       <c r="K393" t="inlineStr">
@@ -25796,13 +25796,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>2885.37</v>
+        <v>805.98</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1233623-512-CM26</t>
+          <t>1233623-486-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -25817,12 +25817,12 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -25861,13 +25861,13 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>3510.5</v>
+        <v>2885.37</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>769-587-CM26</t>
+          <t>1233623-512-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
@@ -25892,12 +25892,12 @@
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25907,12 +25907,12 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K395" t="inlineStr">
@@ -25926,13 +25926,13 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>23360.65</v>
+        <v>3510.5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>2258-6534-CM26</t>
+          <t>769-587-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25957,12 +25957,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25972,17 +25972,17 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -25991,13 +25991,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>25156.69</v>
+        <v>23360.65</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1233623-557-CM26</t>
+          <t>2258-6534-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26012,22 +26012,22 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26037,17 +26037,17 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -26056,13 +26056,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>5088.01</v>
+        <v>25156.69</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1233623-611-CM26</t>
+          <t>1233623-557-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26072,17 +26072,17 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -26121,13 +26121,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>12304.56</v>
+        <v>5088.01</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>697036-60-CM26</t>
+          <t>1233623-611-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26142,7 +26142,7 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
@@ -26152,12 +26152,12 @@
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26186,7 +26186,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>783.0599999999999</v>
+        <v>12304.56</v>
       </c>
     </row>
     <row r="400">
@@ -26257,7 +26257,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>2258-7168-CM26</t>
+          <t>697036-60-CM26</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -26272,22 +26272,22 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G401" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H401" t="inlineStr">
@@ -26297,28 +26297,32 @@
       </c>
       <c r="I401" t="inlineStr">
         <is>
-          <t>Barron Vieyra International Ltda.</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>78.723.570-0</t>
-        </is>
-      </c>
-      <c r="K401" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>5442.39</v>
+        <v>783.0599999999999</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1410-850-CM26</t>
+          <t>2258-7168-CM26</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -26343,12 +26347,12 @@
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H402" t="inlineStr">
@@ -26358,32 +26362,28 @@
       </c>
       <c r="I402" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>Barron Vieyra International Ltda.</t>
         </is>
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K402" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K402" t="inlineStr"/>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>1130.3</v>
+        <v>5442.39</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1410-854-CM26</t>
+          <t>1410-850-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -26398,7 +26398,7 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
@@ -26423,12 +26423,12 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K403" t="inlineStr">
@@ -26442,7 +26442,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>1079.9</v>
+        <v>1130.3</v>
       </c>
     </row>
     <row r="404">
@@ -26513,7 +26513,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1261592-1139-CM26</t>
+          <t>1410-854-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26528,7 +26528,7 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -26538,12 +26538,12 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -26553,17 +26553,17 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L405" t="inlineStr">
@@ -26572,13 +26572,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>39511.4</v>
+        <v>1079.9</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1057384-746-CM26</t>
+          <t>1261592-1139-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26603,12 +26603,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26618,17 +26618,17 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -26637,13 +26637,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>5918.89</v>
+        <v>39511.4</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>993-211-CM26</t>
+          <t>1057384-746-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26658,22 +26658,22 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26702,13 +26702,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>1065.36</v>
+        <v>5918.89</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1233623-604-CM26</t>
+          <t>993-211-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26728,17 +26728,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26767,13 +26767,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>2656.73</v>
+        <v>1065.36</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>2122-200-CM26</t>
+          <t>1233623-604-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26788,22 +26788,22 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26813,17 +26813,17 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L409" t="inlineStr">
@@ -26832,13 +26832,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>1480.84</v>
+        <v>2656.73</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1057385-344-CM26</t>
+          <t>2122-200-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -26853,22 +26853,22 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -26878,17 +26878,17 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L410" t="inlineStr">
@@ -26897,13 +26897,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>1629.03</v>
+        <v>1480.84</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1057385-339-CM26</t>
+          <t>1057385-344-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -26943,17 +26943,17 @@
       </c>
       <c r="I411" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L411" t="inlineStr">
@@ -26962,13 +26962,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>2376.26</v>
+        <v>1629.03</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>697036-67-CM26</t>
+          <t>1057385-339-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -26983,22 +26983,22 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27008,17 +27008,17 @@
       </c>
       <c r="I412" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L412" t="inlineStr">
@@ -27027,13 +27027,13 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>2799.45</v>
+        <v>2376.26</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>650-113-CM26</t>
+          <t>697036-67-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27058,12 +27058,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27092,13 +27092,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2630.04</v>
+        <v>2799.45</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>712-13-CM26</t>
+          <t>650-113-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27113,22 +27113,22 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27157,13 +27157,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>756.33</v>
+        <v>2630.04</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1233623-761-CM26</t>
+          <t>712-13-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27183,17 +27183,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27222,13 +27222,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>3174.26</v>
+        <v>756.33</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>792898-11-CM26</t>
+          <t>1233623-761-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27243,22 +27243,22 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.980.220-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27287,13 +27287,13 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>959.4400000000001</v>
+        <v>3174.26</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>993-222-CM26</t>
+          <t>792898-11-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27308,22 +27308,22 @@
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.220-9</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUPERINTENDENCIA DE EDUCACION ESCOLAR</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27333,17 +27333,17 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L417" t="inlineStr">
@@ -27352,7 +27352,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2194</v>
+        <v>959.4400000000001</v>
       </c>
     </row>
     <row r="418">
@@ -27423,7 +27423,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>2215-1097-CM26</t>
+          <t>993-222-CM26</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -27433,12 +27433,12 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -27448,12 +27448,12 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G419" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H419" t="inlineStr">
@@ -27463,17 +27463,17 @@
       </c>
       <c r="I419" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L419" t="inlineStr">
@@ -27482,13 +27482,13 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>26282.88</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>2215-1062-CM26</t>
+          <t>1233623-786-CM26</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -27513,12 +27513,12 @@
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H420" t="inlineStr">
@@ -27528,12 +27528,12 @@
       </c>
       <c r="I420" t="inlineStr">
         <is>
-          <t>GRUPO DK SERVICIOS LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>76.556.184-1</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K420" t="inlineStr">
@@ -27547,7 +27547,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>3658.34</v>
+        <v>3476.82</v>
       </c>
     </row>
     <row r="421">
@@ -27614,7 +27614,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1233623-786-CM26</t>
+          <t>2215-1062-CM26</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -27639,12 +27639,12 @@
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G422" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H422" t="inlineStr">
@@ -27654,12 +27654,12 @@
       </c>
       <c r="I422" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>GRUPO DK SERVICIOS LIMITADA</t>
         </is>
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.556.184-1</t>
         </is>
       </c>
       <c r="K422" t="inlineStr">
@@ -27673,13 +27673,13 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>3476.82</v>
+        <v>3658.34</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>769-710-CM26</t>
+          <t>2215-1097-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27694,22 +27694,22 @@
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -27719,17 +27719,17 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L423" t="inlineStr">
@@ -27738,13 +27738,13 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>27337.12</v>
+        <v>26282.88</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1171326-56-CM26</t>
+          <t>769-710-CM26</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -27769,12 +27769,12 @@
       </c>
       <c r="F424" t="inlineStr">
         <is>
-          <t>61.926.300-6</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
@@ -27784,12 +27784,12 @@
       </c>
       <c r="I424" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K424" t="inlineStr">
@@ -27803,13 +27803,13 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>1962.84</v>
+        <v>27337.12</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>3846-72-CM26</t>
+          <t>1171326-56-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -27824,22 +27824,22 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.926.300-6</t>
         </is>
       </c>
       <c r="G425" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H425" t="inlineStr">
@@ -27868,7 +27868,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>1246.54</v>
+        <v>1962.84</v>
       </c>
     </row>
     <row r="426">
@@ -27939,7 +27939,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>2258-7681-CM26</t>
+          <t>3846-72-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27954,22 +27954,22 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -27998,13 +27998,13 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>21187.19</v>
+        <v>1246.54</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>3149-315-CM26</t>
+          <t>2258-7681-CM26</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -28019,22 +28019,22 @@
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
         <is>
-          <t>69.253.600-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G428" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H428" t="inlineStr">
@@ -28044,28 +28044,32 @@
       </c>
       <c r="I428" t="inlineStr">
         <is>
-          <t>Francisco javier</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>76.882.403-7</t>
-        </is>
-      </c>
-      <c r="K428" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>73075.14999999999</v>
+        <v>21187.19</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2258-8173-CM26</t>
+          <t>3149-315-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28080,7 +28084,7 @@
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
@@ -28090,12 +28094,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.253.600-2</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MARIA ELENA</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28105,12 +28109,12 @@
       </c>
       <c r="I429" t="inlineStr">
         <is>
-          <t>Barron Vieyra International Ltda.</t>
+          <t>Francisco javier</t>
         </is>
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>78.723.570-0</t>
+          <t>76.882.403-7</t>
         </is>
       </c>
       <c r="K429" t="inlineStr"/>
@@ -28120,13 +28124,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>5138.71</v>
+        <v>73075.14999999999</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>4291-1714-CM26</t>
+          <t>2258-8173-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28141,7 +28145,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -28151,12 +28155,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28166,32 +28170,28 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>Barron Vieyra International Ltda.</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K430" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.723.570-0</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr"/>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>18639.61</v>
+        <v>5138.71</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>769-757-CM26</t>
+          <t>2258-7840-CM26</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -28211,17 +28211,17 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -28231,17 +28231,17 @@
       </c>
       <c r="I431" t="inlineStr">
         <is>
-          <t>ACC INVERSIONES SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>77.786.423-8</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L431" t="inlineStr">
@@ -28250,13 +28250,13 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>14857.02</v>
+        <v>1526.7</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>2258-7840-CM26</t>
+          <t>769-757-CM26</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -28276,17 +28276,17 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G432" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H432" t="inlineStr">
@@ -28296,17 +28296,17 @@
       </c>
       <c r="I432" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>ACC INVERSIONES SPA</t>
         </is>
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>77.786.423-8</t>
         </is>
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L432" t="inlineStr">
@@ -28315,71 +28315,136 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>1526.7</v>
+        <v>14857.02</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
+          <t>4291-1714-CM26</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>70.791.800-4</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M433" s="2" t="n">
+        <v>18639.61</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
           <t>1346284-213-CM26</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
+      <c r="B434" t="inlineStr">
         <is>
           <t>2239-8-LR25</t>
         </is>
       </c>
-      <c r="C433" t="inlineStr">
+      <c r="C434" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
+      <c r="D434" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E433" t="inlineStr">
+      <c r="E434" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F433" t="inlineStr">
+      <c r="F434" t="inlineStr">
         <is>
           <t>62.000.970-9</t>
         </is>
       </c>
-      <c r="G433" t="inlineStr">
+      <c r="G434" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
-      <c r="H433" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I433" t="inlineStr">
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
-      <c r="J433" t="inlineStr">
+      <c r="J434" t="inlineStr">
         <is>
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr">
+      <c r="K434" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L433" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M433" s="2" t="n">
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="n">
         <v>1563.26</v>
       </c>
     </row>

--- a/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
+++ b/docs/oc-regiones/articulos-de-aseo-e-higiene/antofagasta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M434"/>
+  <dimension ref="A1:M435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14812,7 +14812,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1077908-24-CM26</t>
+          <t>1077908-25-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14852,17 +14852,17 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -14871,13 +14871,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>5758.8</v>
+        <v>3105.16</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1077908-25-CM26</t>
+          <t>1077908-24-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14917,17 +14917,17 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -14936,7 +14936,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>3105.16</v>
+        <v>5758.8</v>
       </c>
     </row>
     <row r="226">
@@ -15003,7 +15003,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>752589-1-CM26</t>
+          <t>3858-56-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15023,17 +15023,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.979.490-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15062,13 +15062,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>915.65</v>
+        <v>2982.28</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>3858-56-CM26</t>
+          <t>752589-1-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15088,17 +15088,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.979.490-7</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>UNIDAD ADMINISTRADORA DE LOS TRIBUNALES TRIBUTARIOS Y ADUANEROS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15127,7 +15127,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2982.28</v>
+        <v>915.65</v>
       </c>
     </row>
     <row r="229">
@@ -15328,7 +15328,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>3391-99-CM26</t>
+          <t>3858-61-CM26</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15348,17 +15348,17 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15368,17 +15368,17 @@
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
@@ -15387,13 +15387,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>2026.51</v>
+        <v>47093.88</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>3858-61-CM26</t>
+          <t>3391-99-CM26</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15413,17 +15413,17 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15433,17 +15433,17 @@
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K233" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
@@ -15452,7 +15452,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>47093.88</v>
+        <v>2026.51</v>
       </c>
     </row>
     <row r="234">
@@ -15718,7 +15718,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1346284-26-CM26</t>
+          <t>3391-121-CM26</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15743,12 +15743,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15758,12 +15758,12 @@
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
@@ -15777,13 +15777,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>2839.83</v>
+        <v>876.61</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>3391-121-CM26</t>
+          <t>1346284-26-CM26</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15808,12 +15808,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15823,12 +15823,12 @@
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K239" t="inlineStr">
@@ -15842,7 +15842,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>876.61</v>
+        <v>2839.83</v>
       </c>
     </row>
     <row r="240">
@@ -16498,7 +16498,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>881-29-CM26</t>
+          <t>1057385-47-CM26</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>72.224.100-2</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -16557,7 +16557,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>841.1900000000001</v>
+        <v>2516.7</v>
       </c>
     </row>
     <row r="251">
@@ -16628,7 +16628,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1057385-47-CM26</t>
+          <t>881-29-CM26</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16653,12 +16653,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>72.224.100-2</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16687,7 +16687,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>2516.7</v>
+        <v>841.1900000000001</v>
       </c>
     </row>
     <row r="253">
@@ -17075,7 +17075,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3845-9-CM26</t>
+          <t>4291-152-CM26</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17100,12 +17100,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17134,13 +17134,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4632.84</v>
+        <v>17663.88</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>4291-152-CM26</t>
+          <t>3845-9-CM26</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17165,12 +17165,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17199,7 +17199,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>17663.88</v>
+        <v>4632.84</v>
       </c>
     </row>
     <row r="261">
@@ -17465,7 +17465,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1410-194-CM26</t>
+          <t>1233623-88-CM26</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -17490,12 +17490,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>61.004.007-1</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -17505,12 +17505,12 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -17524,13 +17524,13 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1293.64</v>
+        <v>10239.95</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1233623-88-CM26</t>
+          <t>4291-163-CM26</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -17550,17 +17550,17 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -17570,12 +17570,12 @@
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -17589,13 +17589,13 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>10239.95</v>
+        <v>2777.7</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>4291-163-CM26</t>
+          <t>1410-194-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17615,17 +17615,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>61.004.007-1</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17635,12 +17635,12 @@
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -17654,7 +17654,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>2777.7</v>
+        <v>1293.64</v>
       </c>
     </row>
     <row r="268">
@@ -18306,7 +18306,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>697036-14-CM26</t>
+          <t>3858-122-CM26</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -18331,12 +18331,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -18365,7 +18365,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>795.53</v>
+        <v>2905.72</v>
       </c>
     </row>
     <row r="279">
@@ -18432,7 +18432,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1604-15-CM26</t>
+          <t>3858-123-CM26</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -18452,17 +18452,17 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>60.511.020-7</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -18472,12 +18472,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
@@ -18491,13 +18491,13 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>859.96</v>
+        <v>2368.88</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1057384-229-CM26</t>
+          <t>1604-15-CM26</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18522,12 +18522,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>60.511.020-7</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18537,12 +18537,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
@@ -18556,13 +18556,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1733.21</v>
+        <v>859.96</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>3858-123-CM26</t>
+          <t>1057384-229-CM26</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18582,17 +18582,17 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18602,12 +18602,12 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
@@ -18621,13 +18621,13 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>2368.88</v>
+        <v>1733.21</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>3858-122-CM26</t>
+          <t>697036-14-CM26</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -18652,12 +18652,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18686,13 +18686,13 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>2905.72</v>
+        <v>795.53</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>3858-126-CM26</t>
+          <t>3916-137-CM26</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18712,17 +18712,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>69.020.500-9</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>I MUNICIPALIDAD DE TALTAL</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18732,17 +18732,17 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>MAKRON CHILE SPA</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>78.209.499-8</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -18751,13 +18751,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>4031.63</v>
+        <v>8531.57</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3916-137-CM26</t>
+          <t>3858-126-CM26</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18777,17 +18777,17 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>69.020.500-9</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALTAL</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18797,17 +18797,17 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>MAKRON CHILE SPA</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>78.209.499-8</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
@@ -18816,7 +18816,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>8531.57</v>
+        <v>4031.63</v>
       </c>
     </row>
     <row r="286">
@@ -19338,7 +19338,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>3391-223-CM26</t>
+          <t>3391-222-CM26</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -19397,13 +19397,13 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1951.06</v>
+        <v>1701.36</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>3391-222-CM26</t>
+          <t>3391-223-CM26</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19462,13 +19462,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>1701.36</v>
+        <v>1951.06</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2258-2707-CM26</t>
+          <t>1233623-118-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19493,12 +19493,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19527,13 +19527,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>765.7</v>
+        <v>41354.92</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1233623-118-CM26</t>
+          <t>2258-2707-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19558,12 +19558,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19592,7 +19592,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>41354.92</v>
+        <v>765.7</v>
       </c>
     </row>
     <row r="298">
@@ -19854,7 +19854,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>2429-346-CM26</t>
+          <t>2429-333-CM26</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -19874,7 +19874,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -19894,32 +19894,28 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr"/>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>25562.66</v>
+        <v>35542.28</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>2429-333-CM26</t>
+          <t>2429-346-CM26</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -19939,7 +19935,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -19959,22 +19955,26 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
-        </is>
-      </c>
-      <c r="K303" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>35542.28</v>
+        <v>25562.66</v>
       </c>
     </row>
     <row r="304">
@@ -20045,7 +20045,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1057384-328-CM26</t>
+          <t>1233623-128-CM26</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -20065,17 +20065,17 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -20104,13 +20104,13 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>6142.49</v>
+        <v>13901.14</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1233623-128-CM26</t>
+          <t>1057384-328-CM26</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -20130,17 +20130,17 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -20169,7 +20169,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>13901.14</v>
+        <v>6142.49</v>
       </c>
     </row>
     <row r="307">
@@ -20435,7 +20435,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1425773-37-CM26</t>
+          <t>3391-269-CM26</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -20455,17 +20455,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>88.951.800-6</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -20475,22 +20475,26 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA VYB</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>76.583.494-5</t>
-        </is>
-      </c>
-      <c r="K311" t="inlineStr"/>
+          <t>96.556.940-5</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>3765.92</v>
+        <v>1723.02</v>
       </c>
     </row>
     <row r="312">
@@ -20561,7 +20565,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>3391-269-CM26</t>
+          <t>1425773-37-CM26</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -20581,17 +20585,17 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>88.951.800-6</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP CULTURAL Y TURISMO DE CALAMA</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -20601,26 +20605,22 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIALIZADORA VYB</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
-        </is>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.583.494-5</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr"/>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>1723.02</v>
+        <v>3765.92</v>
       </c>
     </row>
     <row r="314">
@@ -21077,7 +21077,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>4291-473-CM26</t>
+          <t>3846-40-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -21102,12 +21102,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>70.791.800-4</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -21136,7 +21136,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>4970.25</v>
+        <v>5074.29</v>
       </c>
     </row>
     <row r="322">
@@ -21207,7 +21207,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>3846-40-CM26</t>
+          <t>4291-473-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21232,12 +21232,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>70.791.800-4</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>UNIVERSIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21266,13 +21266,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5074.29</v>
+        <v>4970.25</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2429-517-CM26</t>
+          <t>2215-586-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21297,12 +21297,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21312,28 +21312,32 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr"/>
+          <t>76.287.853-4</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>28314.25</v>
+        <v>12129.19</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2215-586-CM26</t>
+          <t>2429-517-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21358,12 +21362,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21373,26 +21377,22 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>12129.19</v>
+        <v>28314.25</v>
       </c>
     </row>
     <row r="326">
@@ -21463,7 +21463,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>3834-139-CM26</t>
+          <t>2258-4335-CM26</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -21488,12 +21488,12 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -21503,17 +21503,17 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -21522,13 +21522,13 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4736.63</v>
+        <v>1151.17</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2258-4335-CM26</t>
+          <t>3834-139-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -21553,12 +21553,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -21568,17 +21568,17 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -21587,7 +21587,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1151.17</v>
+        <v>4736.63</v>
       </c>
     </row>
     <row r="329">
@@ -21723,7 +21723,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1499684-25-CM26</t>
+          <t>1057385-159-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21743,17 +21743,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>65.077.905-3</t>
+          <t>61.606.204-2</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>FUNDACION DE CULTURA DE SAN PEDRO DE ATACAMA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -21763,17 +21763,17 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -21782,7 +21782,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>941.3</v>
+        <v>844.88</v>
       </c>
     </row>
     <row r="332">
@@ -21853,7 +21853,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1057385-159-CM26</t>
+          <t>1499684-25-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21873,17 +21873,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>61.606.204-2</t>
+          <t>65.077.905-3</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL 21 DE MAYO TALTAL</t>
+          <t>FUNDACION DE CULTURA DE SAN PEDRO DE ATACAMA</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21893,17 +21893,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21912,7 +21912,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>844.88</v>
+        <v>941.3</v>
       </c>
     </row>
     <row r="334">
@@ -23080,7 +23080,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>769-438-CM26</t>
+          <t>2258-5351-CM26</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -23105,12 +23105,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -23120,12 +23120,12 @@
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t>ACC INVERSIONES SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>77.786.423-8</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K352" t="inlineStr">
@@ -23139,13 +23139,13 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>20759.6</v>
+        <v>24827.51</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2258-5351-CM26</t>
+          <t>769-438-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -23170,12 +23170,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -23185,12 +23185,12 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>ACC INVERSIONES SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.786.423-8</t>
         </is>
       </c>
       <c r="K353" t="inlineStr">
@@ -23204,7 +23204,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>24827.51</v>
+        <v>20759.6</v>
       </c>
     </row>
     <row r="354">
@@ -24307,7 +24307,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>2215-807-CM26</t>
+          <t>3858-321-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -24327,17 +24327,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>61.606.202-6</t>
+          <t>69.020.400-2</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -24347,17 +24347,17 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
@@ -24366,7 +24366,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>45781.56</v>
+        <v>4988.22</v>
       </c>
     </row>
     <row r="372">
@@ -24502,7 +24502,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>3858-321-CM26</t>
+          <t>2215-807-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -24522,17 +24522,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.020.400-2</t>
+          <t>61.606.202-6</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSP C CIS</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -24542,17 +24542,17 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -24561,7 +24561,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>4988.22</v>
+        <v>45781.56</v>
       </c>
     </row>
     <row r="375">
@@ -25087,7 +25087,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1233623-416-CM26</t>
+          <t>3391-508-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25107,17 +25107,17 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H383" t="inlineStr">
@@ -25127,17 +25127,17 @@
       </c>
       <c r="I383" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L383" t="inlineStr">
@@ -25146,7 +25146,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>5053.31</v>
+        <v>9726.92</v>
       </c>
     </row>
     <row r="384">
@@ -25347,7 +25347,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>3391-508-CM26</t>
+          <t>1233623-416-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25367,17 +25367,17 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25387,17 +25387,17 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -25406,13 +25406,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>9726.92</v>
+        <v>5053.31</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>3845-55-CM26</t>
+          <t>1079454-361-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25437,12 +25437,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>61.978.660-2</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25452,17 +25452,17 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
@@ -25471,13 +25471,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>3432.54</v>
+        <v>1117.66</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1079454-361-CM26</t>
+          <t>3845-55-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25502,12 +25502,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.978.660-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25517,17 +25517,17 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
@@ -25536,7 +25536,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>1117.66</v>
+        <v>3432.54</v>
       </c>
     </row>
     <row r="390">
@@ -25932,7 +25932,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>769-587-CM26</t>
+          <t>2258-6534-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -25957,12 +25957,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.606.200-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -25972,17 +25972,17 @@
       </c>
       <c r="I396" t="inlineStr">
         <is>
-          <t>JIREH SOLUTION SPA</t>
+          <t>DIMERC S A</t>
         </is>
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>78.061.716-0</t>
+          <t>96.670.840-9</t>
         </is>
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="L396" t="inlineStr">
@@ -25991,13 +25991,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>23360.65</v>
+        <v>25156.69</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>2258-6534-CM26</t>
+          <t>769-587-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26022,12 +26022,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.606.200-k</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA DIRECCION</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26037,17 +26037,17 @@
       </c>
       <c r="I397" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>JIREH SOLUTION SPA</t>
         </is>
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>78.061.716-0</t>
         </is>
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L397" t="inlineStr">
@@ -26056,7 +26056,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>25156.69</v>
+        <v>23360.65</v>
       </c>
     </row>
     <row r="398">
@@ -26578,7 +26578,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1261592-1139-CM26</t>
+          <t>1057384-746-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26603,12 +26603,12 @@
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>61.606.203-4</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26618,17 +26618,17 @@
       </c>
       <c r="I406" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L406" t="inlineStr">
@@ -26637,13 +26637,13 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>39511.4</v>
+        <v>5918.89</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1057384-746-CM26</t>
+          <t>1261592-1139-CM26</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -26668,12 +26668,12 @@
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>61.606.203-4</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G407" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL M</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H407" t="inlineStr">
@@ -26683,17 +26683,17 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L407" t="inlineStr">
@@ -26702,13 +26702,13 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>5918.89</v>
+        <v>39511.4</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>993-211-CM26</t>
+          <t>1233623-604-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -26728,17 +26728,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26767,13 +26767,13 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>1065.36</v>
+        <v>2656.73</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1233623-604-CM26</t>
+          <t>993-211-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26793,17 +26793,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26832,7 +26832,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>2656.73</v>
+        <v>1065.36</v>
       </c>
     </row>
     <row r="410">
@@ -27033,7 +27033,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>697036-67-CM26</t>
+          <t>650-113-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27058,12 +27058,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>61.814.000-8</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27092,13 +27092,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>2799.45</v>
+        <v>2630.04</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>650-113-CM26</t>
+          <t>697036-67-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27123,12 +27123,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.814.000-8</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION II REGION</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27157,13 +27157,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>2630.04</v>
+        <v>2799.45</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>712-13-CM26</t>
+          <t>1233623-761-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27183,17 +27183,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27222,13 +27222,13 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>756.33</v>
+        <v>3174.26</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1233623-761-CM26</t>
+          <t>712-13-CM26</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -27248,17 +27248,17 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>3174.26</v>
+        <v>756.33</v>
       </c>
     </row>
     <row r="417">
@@ -27874,7 +27874,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1261592-1284-CM26</t>
+          <t>3846-72-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -27894,17 +27894,17 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>71.102.600-2</t>
+          <t>69.253.200-7</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
+          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
@@ -27914,17 +27914,17 @@
       </c>
       <c r="I426" t="inlineStr">
         <is>
-          <t>COMERCIAL RED OFFICE LIMITADA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>77.012.870-6</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L426" t="inlineStr">
@@ -27933,13 +27933,13 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>339103.42</v>
+        <v>1246.54</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>3846-72-CM26</t>
+          <t>1261592-1284-CM26</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -27959,17 +27959,17 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>69.253.200-7</t>
+          <t>71.102.600-2</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SIERRA GORDA</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -27979,17 +27979,17 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>COMERCIAL RED OFFICE LIMITADA</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>77.012.870-6</t>
         </is>
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="L427" t="inlineStr">
@@ -27998,7 +27998,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>1246.54</v>
+        <v>339103.42</v>
       </c>
     </row>
     <row r="428">
@@ -28386,65 +28386,130 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
+          <t>3858-475-CM26</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2239-8-LR25</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>69.020.400-2</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE MEJILLONES</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>EVENTAIL SPA</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="n">
+        <v>3107.22</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
           <t>1346284-213-CM26</t>
         </is>
       </c>
-      <c r="B434" t="inlineStr">
+      <c r="B435" t="inlineStr">
         <is>
           <t>2239-8-LR25</t>
         </is>
       </c>
-      <c r="C434" t="inlineStr">
+      <c r="C435" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D434" t="inlineStr">
+      <c r="D435" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="E434" t="inlineStr">
+      <c r="E435" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F434" t="inlineStr">
+      <c r="F435" t="inlineStr">
         <is>
           <t>62.000.970-9</t>
         </is>
       </c>
-      <c r="G434" t="inlineStr">
+      <c r="G435" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
-      <c r="H434" t="inlineStr">
-        <is>
-          <t>Antofagasta</t>
-        </is>
-      </c>
-      <c r="I434" t="inlineStr">
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
         <is>
           <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
-      <c r="J434" t="inlineStr">
+      <c r="J435" t="inlineStr">
         <is>
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr">
+      <c r="K435" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L434" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M434" s="2" t="n">
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="n">
         <v>1563.26</v>
       </c>
     </row>
